--- a/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/制造_躯体材料配置表_Manufacture_BodyPartConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/制造_躯体材料配置表_Manufacture_BodyPartConfig.xlsx
@@ -32,11 +32,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="742" uniqueCount="231">
   <si>
     <t>躯体ID</t>
   </si>
   <si>
+    <t>道具名称</t>
+  </si>
+  <si>
     <t>躯体等级</t>
   </si>
   <si>
@@ -73,48 +76,54 @@
     <t>躯体主属性</t>
   </si>
   <si>
-    <t>主键；与 MaterialId 同命名空间不得冲突</t>
-  </si>
-  <si>
-    <t>≥0；参与外观平均等级</t>
-  </si>
-  <si>
-    <t>Head|Torso|Arm|Leg</t>
-  </si>
-  <si>
-    <t>FK → RaceConfig</t>
-  </si>
-  <si>
-    <t>≥0</t>
-  </si>
-  <si>
-    <t>≥0；Mode2 AutoManufacture 不计</t>
-  </si>
-  <si>
-    <t>属性项_数值|…；计入 Base(S)</t>
-  </si>
-  <si>
-    <t>每 1 超出兑精魂数</t>
-  </si>
-  <si>
-    <t>展示文案</t>
-  </si>
-  <si>
-    <t>仓库 / DigReward 可用</t>
-  </si>
-  <si>
-    <t>仅 Arm；1=Mode2 选料锚点；缺省 0</t>
-  </si>
-  <si>
-    <t>ClassId|…；Mode2 双手定职业</t>
-  </si>
-  <si>
-    <t>Strength|Agility|Intelligence；Mode2 选料匹配</t>
+    <t>主键；可被 LootDrop / 仓库引用；与 MaterialId 同命名空间不得冲突</t>
+  </si>
+  <si>
+    <t>仓库 / DigStageSummary 展示名；未启用 i18n 时直接当展示串；空则 UI 回退 BodyPartId</t>
+  </si>
+  <si>
+    <t>≥0；参与制造时外观平均等级</t>
+  </si>
+  <si>
+    <t>Head / Torso / Arm / Leg</t>
+  </si>
+  <si>
+    <t>FK → RaceConfig；参与加权定种族</t>
+  </si>
+  <si>
+    <t>≥0；计入制造 BodyCost</t>
+  </si>
+  <si>
+    <t>≥0；缺省 0；计入制造总精魂消耗</t>
+  </si>
+  <si>
+    <t>五项基础属性平坦加成；制造时按维 Σ 得 Base(S)</t>
+  </si>
+  <si>
+    <t>每 1 个超出材料兑精魂数；0=超出丢弃且不兑</t>
+  </si>
+  <si>
+    <t>展示文案；若启用 i18n 可为本地化 Key</t>
+  </si>
+  <si>
+    <t>部位单件外观 / 仓库 UI 可用资源 Id</t>
+  </si>
+  <si>
+    <t>仅 Arm 有意义；1=主要手（Mode2 选料锚点）；缺省 0</t>
+  </si>
+  <si>
+    <t>可产出的 ClassId 多值；Mode2 双手交集定职业</t>
+  </si>
+  <si>
+    <t>Strength | Agility | Intelligence；Mode2 选其余部位匹配键</t>
   </si>
   <si>
     <t>BodyPartId</t>
   </si>
   <si>
+    <t>DisplayName</t>
+  </si>
+  <si>
     <t>BodyLevel</t>
   </si>
   <si>
@@ -154,15 +163,18 @@
     <t>BP_Head_Human</t>
   </si>
   <si>
+    <t>人类头部</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
     <t>Head</t>
   </si>
   <si>
     <t>Race_Human</t>
   </si>
   <si>
-    <t>1</t>
-  </si>
-  <si>
     <t>MaxHP_20|Strength_8|Agility_16|Intelligence_24|MoveSpeed_0.1</t>
   </si>
   <si>
@@ -184,6 +196,9 @@
     <t>BP_Torso_Human</t>
   </si>
   <si>
+    <t>人类躯干</t>
+  </si>
+  <si>
     <t>Torso</t>
   </si>
   <si>
@@ -202,6 +217,9 @@
     <t>BP_Arm_Human</t>
   </si>
   <si>
+    <t>人类手臂</t>
+  </si>
+  <si>
     <t>Arm</t>
   </si>
   <si>
@@ -220,6 +238,9 @@
     <t>BP_Arm_Elf</t>
   </si>
   <si>
+    <t>精灵手臂</t>
+  </si>
+  <si>
     <t>Race_Elf</t>
   </si>
   <si>
@@ -241,6 +262,9 @@
     <t>BP_Arm_Orc</t>
   </si>
   <si>
+    <t>兽人手臂</t>
+  </si>
+  <si>
     <t>Race_Orc</t>
   </si>
   <si>
@@ -250,6 +274,9 @@
     <t>BP_Arm_Undead</t>
   </si>
   <si>
+    <t>亡灵手臂</t>
+  </si>
+  <si>
     <t>Race_Undead</t>
   </si>
   <si>
@@ -259,6 +286,9 @@
     <t>BP_Arm_Dwarf</t>
   </si>
   <si>
+    <t>矮人手臂</t>
+  </si>
+  <si>
     <t>Race_Dwarf</t>
   </si>
   <si>
@@ -268,6 +298,9 @@
     <t>BP_Arm_Goblin</t>
   </si>
   <si>
+    <t>地精手臂</t>
+  </si>
+  <si>
     <t>Race_Goblin</t>
   </si>
   <si>
@@ -277,6 +310,9 @@
     <t>BP_Arm_Demon</t>
   </si>
   <si>
+    <t>恶魔手臂</t>
+  </si>
+  <si>
     <t>Race_Demon</t>
   </si>
   <si>
@@ -286,6 +322,9 @@
     <t>BP_Arm_Angel</t>
   </si>
   <si>
+    <t>天使手臂</t>
+  </si>
+  <si>
     <t>Race_Angel</t>
   </si>
   <si>
@@ -295,6 +334,9 @@
     <t>BP_Arm_Beast</t>
   </si>
   <si>
+    <t>野兽手臂</t>
+  </si>
+  <si>
     <t>Race_Beast</t>
   </si>
   <si>
@@ -304,6 +346,9 @@
     <t>BP_Arm_Construct</t>
   </si>
   <si>
+    <t>构装体手臂</t>
+  </si>
+  <si>
     <t>Race_Construct</t>
   </si>
   <si>
@@ -337,6 +382,9 @@
     <t>BP_Leg_Elf</t>
   </si>
   <si>
+    <t>精灵腿部</t>
+  </si>
+  <si>
     <t>Leg</t>
   </si>
   <si>
@@ -352,6 +400,9 @@
     <t>BP_Head_Orc</t>
   </si>
   <si>
+    <t>兽人头部</t>
+  </si>
+  <si>
     <t>MaxHP_40|Strength_8|Agility_16|Intelligence_24|MoveSpeed_0.2</t>
   </si>
   <si>
@@ -364,6 +415,9 @@
     <t>BP_Torso_Orc</t>
   </si>
   <si>
+    <t>兽人躯干</t>
+  </si>
+  <si>
     <t>MaxHP_45|Strength_16|Agility_24|Intelligence_4|MoveSpeed_0.3</t>
   </si>
   <si>
@@ -376,6 +430,9 @@
     <t>BP_Leg_Dwarf</t>
   </si>
   <si>
+    <t>矮人腿部</t>
+  </si>
+  <si>
     <t>MaxHP_55|Strength_4|Agility_8|Intelligence_16|MoveSpeed_0.2</t>
   </si>
   <si>
@@ -388,6 +445,9 @@
     <t>BP_Head_Demon</t>
   </si>
   <si>
+    <t>恶魔头部</t>
+  </si>
+  <si>
     <t>MaxHP_60|Strength_8|Agility_16|Intelligence_24|MoveSpeed_0.3</t>
   </si>
   <si>
@@ -400,6 +460,9 @@
     <t>BP_Torso_Angel</t>
   </si>
   <si>
+    <t>天使躯干</t>
+  </si>
+  <si>
     <t>MaxHP_65|Strength_16|Agility_24|Intelligence_4|MoveSpeed_0.1</t>
   </si>
   <si>
@@ -407,6 +470,261 @@
   </si>
   <si>
     <t>Art_BP_Torso_Angel</t>
+  </si>
+  <si>
+    <t>BP_Head_Undead_1</t>
+  </si>
+  <si>
+    <t>亡灵头部</t>
+  </si>
+  <si>
+    <t>Art_BP_Head_Undead_1</t>
+  </si>
+  <si>
+    <t>BP_Torso_Undead_1</t>
+  </si>
+  <si>
+    <t>亡灵躯干</t>
+  </si>
+  <si>
+    <t>Art_BP_Torso_Undead_1</t>
+  </si>
+  <si>
+    <t>BP_Arm_Undead_Warrior</t>
+  </si>
+  <si>
+    <t>战士</t>
+  </si>
+  <si>
+    <t>Art_BP_Arm_Undead_Warrior</t>
+  </si>
+  <si>
+    <t>BP_Arm_Undead_Archer</t>
+  </si>
+  <si>
+    <t>射手</t>
+  </si>
+  <si>
+    <t>Art_BP_Arm_Undead_Archer</t>
+  </si>
+  <si>
+    <t>BP_Arm_Undead_Mage</t>
+  </si>
+  <si>
+    <t>法师</t>
+  </si>
+  <si>
+    <t>Art_BP_Arm_Undead_Mage</t>
+  </si>
+  <si>
+    <t>BP_Arm_Undead_Rogue</t>
+  </si>
+  <si>
+    <t>盗贼</t>
+  </si>
+  <si>
+    <t>Art_BP_Arm_Undead_Rogue</t>
+  </si>
+  <si>
+    <t>BP_Arm_Undead_Guardian</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>近卫</t>
+  </si>
+  <si>
+    <t>Art_BP_Arm_Undead_Guardian</t>
+  </si>
+  <si>
+    <t>Class_Guardian</t>
+  </si>
+  <si>
+    <t>BP_Arm_Undead_BombMaster</t>
+  </si>
+  <si>
+    <t>炸弹师</t>
+  </si>
+  <si>
+    <t>Art_BP_Arm_Undead_BombMaster</t>
+  </si>
+  <si>
+    <t>Class_BombMaster</t>
+  </si>
+  <si>
+    <t>BP_Arm_Undead_IceMage</t>
+  </si>
+  <si>
+    <t>冰法</t>
+  </si>
+  <si>
+    <t>Art_BP_Arm_Undead_IceMage</t>
+  </si>
+  <si>
+    <t>Class_IceMage</t>
+  </si>
+  <si>
+    <t>BP_Arm_Undead_Brawler</t>
+  </si>
+  <si>
+    <t>格斗师</t>
+  </si>
+  <si>
+    <t>Art_BP_Arm_Undead_Brawler</t>
+  </si>
+  <si>
+    <t>Class_Brawler</t>
+  </si>
+  <si>
+    <t>BP_Arm_Undead_Berserker</t>
+  </si>
+  <si>
+    <t>狂战士</t>
+  </si>
+  <si>
+    <t>Art_BP_Arm_Undead_Berserker</t>
+  </si>
+  <si>
+    <t>BP_Arm_Undead_Longbowman</t>
+  </si>
+  <si>
+    <t>长弓手</t>
+  </si>
+  <si>
+    <t>Art_BP_Arm_Undead_Longbowman</t>
+  </si>
+  <si>
+    <t>Class_Longbowman</t>
+  </si>
+  <si>
+    <t>BP_Arm_Undead_FireMage</t>
+  </si>
+  <si>
+    <t>火法</t>
+  </si>
+  <si>
+    <t>Art_BP_Arm_Undead_FireMage</t>
+  </si>
+  <si>
+    <t>Class_FireMage</t>
+  </si>
+  <si>
+    <t>BP_Arm_Undead_Shadowblade</t>
+  </si>
+  <si>
+    <t>影刃</t>
+  </si>
+  <si>
+    <t>Art_BP_Arm_Undead_Shadowblade</t>
+  </si>
+  <si>
+    <t>Class_Shadowblade</t>
+  </si>
+  <si>
+    <t>BP_Arm_Angel_Paladin</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>圣骑士</t>
+  </si>
+  <si>
+    <t>Art_BP_Arm_Angel_Paladin</t>
+  </si>
+  <si>
+    <t>BP_Arm_Demon_DarkMage</t>
+  </si>
+  <si>
+    <t>暗黑法师</t>
+  </si>
+  <si>
+    <t>Art_BP_Arm_Demon_DarkMage</t>
+  </si>
+  <si>
+    <t>Class_DarkMage</t>
+  </si>
+  <si>
+    <t>BP_Arm_Undead_1</t>
+  </si>
+  <si>
+    <t>Art_BP_Arm_Undead_1</t>
+  </si>
+  <si>
+    <t>BP_Leg_Undead_1</t>
+  </si>
+  <si>
+    <t>亡灵腿部</t>
+  </si>
+  <si>
+    <t>Art_BP_Leg_Undead_1</t>
+  </si>
+  <si>
+    <t>BP_Head_Undead_2</t>
+  </si>
+  <si>
+    <t>Art_BP_Head_Undead_2</t>
+  </si>
+  <si>
+    <t>BP_Torso_Undead_2</t>
+  </si>
+  <si>
+    <t>Art_BP_Torso_Undead_2</t>
+  </si>
+  <si>
+    <t>BP_Arm_Undead_2</t>
+  </si>
+  <si>
+    <t>Art_BP_Arm_Undead_2</t>
+  </si>
+  <si>
+    <t>BP_Leg_Undead_2</t>
+  </si>
+  <si>
+    <t>Art_BP_Leg_Undead_2</t>
+  </si>
+  <si>
+    <t>BP_Head_Angel</t>
+  </si>
+  <si>
+    <t>天使头部</t>
+  </si>
+  <si>
+    <t>Art_BP_Head_Angel</t>
+  </si>
+  <si>
+    <t>Art_BP_Arm_Angel</t>
+  </si>
+  <si>
+    <t>BP_Leg_Angel</t>
+  </si>
+  <si>
+    <t>天使腿部</t>
+  </si>
+  <si>
+    <t>Art_BP_Leg_Angel</t>
+  </si>
+  <si>
+    <t>BP_Torso_Demon</t>
+  </si>
+  <si>
+    <t>恶魔躯干</t>
+  </si>
+  <si>
+    <t>Art_BP_Torso_Demon</t>
+  </si>
+  <si>
+    <t>Art_BP_Arm_Demon</t>
+  </si>
+  <si>
+    <t>BP_Leg_Demon</t>
+  </si>
+  <si>
+    <t>恶魔腿部</t>
+  </si>
+  <si>
+    <t>Art_BP_Leg_Demon</t>
   </si>
 </sst>
 </file>
@@ -579,7 +897,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -589,6 +907,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -909,7 +1233,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -933,16 +1257,16 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -951,92 +1275,92 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1383,14 +1707,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M23"/>
+  <dimension ref="A1:N53"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
-  <cols>
-    <col min="1" max="1" width="18.75" customWidth="1"/>
-    <col min="4" max="4" width="16.25" customWidth="1"/>
-  </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:14">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1430,907 +1750,2296 @@
       <c r="M1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:13">
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="3" s="1" customFormat="1" spans="1:13">
+        <v>26</v>
+      </c>
+      <c r="N2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" spans="1:14">
       <c r="A3" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4" t="s">
         <v>40</v>
       </c>
-      <c r="D4" t="s">
+      <c r="N3" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="E4" t="s">
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-      <c r="G4" t="s">
+      <c r="B4" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="H4" t="s">
-        <v>42</v>
-      </c>
-      <c r="I4" t="s">
-        <v>44</v>
-      </c>
-      <c r="J4" t="s">
+      <c r="C4" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="K4" t="s">
+      <c r="E4" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="L4" t="s">
+      <c r="F4" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="H4" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="M4" t="s">
+      <c r="I4" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="J4" s="2" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" t="s">
+      <c r="K4" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="L4" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="D5" t="s">
-        <v>41</v>
-      </c>
-      <c r="E5" t="s">
-        <v>42</v>
-      </c>
-      <c r="F5">
-        <v>1</v>
-      </c>
-      <c r="G5" t="s">
+      <c r="M4" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="H5" t="s">
-        <v>42</v>
-      </c>
-      <c r="I5" t="s">
+      <c r="N4" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="J5" t="s">
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="K5" t="s">
+      <c r="B5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="L5" t="s">
-        <v>47</v>
-      </c>
-      <c r="M5" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" t="s">
-        <v>55</v>
-      </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="C6" t="s">
+      <c r="F5" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="H5" s="2" t="s">
         <v>56</v>
       </c>
+      <c r="I5" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="N5" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="A6" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>44</v>
+      </c>
       <c r="D6" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E6" t="s">
-        <v>42</v>
-      </c>
-      <c r="F6">
-        <v>1</v>
-      </c>
-      <c r="G6" t="s">
-        <v>57</v>
-      </c>
-      <c r="H6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I6" t="s">
-        <v>58</v>
-      </c>
-      <c r="J6" t="s">
+        <v>62</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="M6" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="N6" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="K6" t="s">
-        <v>42</v>
-      </c>
-      <c r="L6" t="s">
-        <v>60</v>
-      </c>
-      <c r="M6" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" t="s">
-        <v>61</v>
-      </c>
-      <c r="B7">
-        <v>1</v>
-      </c>
-      <c r="C7" t="s">
-        <v>56</v>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="A7" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="E7" t="s">
-        <v>42</v>
-      </c>
-      <c r="F7">
-        <v>1</v>
-      </c>
-      <c r="G7" t="s">
+      <c r="E7" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="N7" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="M8" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="N8" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="N9" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="M10" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="N10" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="M11" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="N11" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="M12" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="N12" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="M13" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="N13" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="A14" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="M14" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="N14" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="A15" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="M15" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="N15" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="A16" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="M16" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="N16" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
+      <c r="A17" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="K17" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="L17" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="M17" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="N17" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14">
+      <c r="A18" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="L18" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="M18" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="N18" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14">
+      <c r="A19" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="L19" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="M19" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="N19" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14">
+      <c r="A20" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="K20" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="L20" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="M20" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="N20" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14">
+      <c r="A21" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="K21" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="L21" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="M21" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="N21" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14">
+      <c r="A22" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="K22" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="L22" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="M22" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="N22" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14">
+      <c r="A23" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="K23" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="L23" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="M23" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="N23" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14">
+      <c r="A24" t="s">
+        <v>146</v>
+      </c>
+      <c r="B24" t="s">
+        <v>147</v>
+      </c>
+      <c r="C24" t="s">
+        <v>44</v>
+      </c>
+      <c r="D24" t="s">
+        <v>45</v>
+      </c>
+      <c r="E24" t="s">
+        <v>81</v>
+      </c>
+      <c r="F24" t="s">
+        <v>44</v>
+      </c>
+      <c r="G24" t="s">
+        <v>44</v>
+      </c>
+      <c r="H24" t="s">
+        <v>47</v>
+      </c>
+      <c r="I24" t="s">
+        <v>44</v>
+      </c>
+      <c r="J24" t="s">
+        <v>51</v>
+      </c>
+      <c r="K24" t="s">
+        <v>148</v>
+      </c>
+      <c r="L24" t="s">
+        <v>50</v>
+      </c>
+      <c r="M24" t="s">
+        <v>51</v>
+      </c>
+      <c r="N24" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14">
+      <c r="A25" t="s">
+        <v>149</v>
+      </c>
+      <c r="B25" t="s">
+        <v>150</v>
+      </c>
+      <c r="C25" t="s">
+        <v>44</v>
+      </c>
+      <c r="D25" t="s">
+        <v>55</v>
+      </c>
+      <c r="E25" t="s">
+        <v>81</v>
+      </c>
+      <c r="F25" t="s">
+        <v>44</v>
+      </c>
+      <c r="G25" t="s">
+        <v>44</v>
+      </c>
+      <c r="H25" t="s">
+        <v>56</v>
+      </c>
+      <c r="I25" t="s">
+        <v>44</v>
+      </c>
+      <c r="J25" t="s">
+        <v>51</v>
+      </c>
+      <c r="K25" t="s">
+        <v>151</v>
+      </c>
+      <c r="L25" t="s">
+        <v>50</v>
+      </c>
+      <c r="M25" t="s">
+        <v>51</v>
+      </c>
+      <c r="N25" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14">
+      <c r="A26" t="s">
+        <v>152</v>
+      </c>
+      <c r="B26" t="s">
+        <v>80</v>
+      </c>
+      <c r="C26" t="s">
+        <v>44</v>
+      </c>
+      <c r="D26" t="s">
+        <v>62</v>
+      </c>
+      <c r="E26" t="s">
+        <v>81</v>
+      </c>
+      <c r="F26" t="s">
+        <v>44</v>
+      </c>
+      <c r="G26" t="s">
+        <v>44</v>
+      </c>
+      <c r="H26" t="s">
         <v>63</v>
       </c>
-      <c r="H7" t="s">
-        <v>42</v>
-      </c>
-      <c r="I7" t="s">
-        <v>64</v>
-      </c>
-      <c r="J7" t="s">
-        <v>65</v>
-      </c>
-      <c r="K7" t="s">
-        <v>42</v>
-      </c>
-      <c r="L7" t="s">
+      <c r="I26" t="s">
+        <v>44</v>
+      </c>
+      <c r="J26" t="s">
+        <v>153</v>
+      </c>
+      <c r="K26" t="s">
+        <v>154</v>
+      </c>
+      <c r="L26" t="s">
+        <v>44</v>
+      </c>
+      <c r="M26" t="s">
         <v>66</v>
       </c>
-      <c r="M7" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" t="s">
-        <v>68</v>
-      </c>
-      <c r="B8">
-        <v>1</v>
-      </c>
-      <c r="C8" t="s">
-        <v>56</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="E8" t="s">
-        <v>42</v>
-      </c>
-      <c r="F8">
-        <v>1</v>
-      </c>
-      <c r="G8" t="s">
-        <v>63</v>
-      </c>
-      <c r="H8" t="s">
-        <v>42</v>
-      </c>
-      <c r="I8" t="s">
-        <v>64</v>
-      </c>
-      <c r="J8" t="s">
-        <v>65</v>
-      </c>
-      <c r="K8" t="s">
-        <v>42</v>
-      </c>
-      <c r="L8" t="s">
+      <c r="N26" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14">
+      <c r="A27" t="s">
+        <v>155</v>
+      </c>
+      <c r="B27" t="s">
+        <v>80</v>
+      </c>
+      <c r="C27" t="s">
+        <v>44</v>
+      </c>
+      <c r="D27" t="s">
+        <v>62</v>
+      </c>
+      <c r="E27" t="s">
+        <v>81</v>
+      </c>
+      <c r="F27" t="s">
+        <v>44</v>
+      </c>
+      <c r="G27" t="s">
+        <v>44</v>
+      </c>
+      <c r="H27" t="s">
         <v>70</v>
       </c>
-      <c r="M8" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" t="s">
-        <v>71</v>
-      </c>
-      <c r="B9">
-        <v>1</v>
-      </c>
-      <c r="C9" t="s">
-        <v>56</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E9" t="s">
-        <v>42</v>
-      </c>
-      <c r="F9">
-        <v>1</v>
-      </c>
-      <c r="G9" t="s">
-        <v>63</v>
-      </c>
-      <c r="H9" t="s">
-        <v>42</v>
-      </c>
-      <c r="I9" t="s">
-        <v>64</v>
-      </c>
-      <c r="J9" t="s">
-        <v>65</v>
-      </c>
-      <c r="K9" t="s">
-        <v>42</v>
-      </c>
-      <c r="L9" t="s">
+      <c r="I27" t="s">
+        <v>44</v>
+      </c>
+      <c r="J27" t="s">
+        <v>156</v>
+      </c>
+      <c r="K27" t="s">
+        <v>157</v>
+      </c>
+      <c r="L27" t="s">
+        <v>44</v>
+      </c>
+      <c r="M27" t="s">
         <v>73</v>
       </c>
-      <c r="M9" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="A10" t="s">
+      <c r="N27" t="s">
         <v>74</v>
       </c>
-      <c r="B10">
-        <v>1</v>
-      </c>
-      <c r="C10" t="s">
-        <v>56</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="E10" t="s">
-        <v>42</v>
-      </c>
-      <c r="F10">
-        <v>1</v>
-      </c>
-      <c r="G10" t="s">
-        <v>63</v>
-      </c>
-      <c r="H10" t="s">
-        <v>42</v>
-      </c>
-      <c r="I10" t="s">
-        <v>64</v>
-      </c>
-      <c r="J10" t="s">
-        <v>65</v>
-      </c>
-      <c r="K10" t="s">
-        <v>42</v>
-      </c>
-      <c r="L10" t="s">
-        <v>76</v>
-      </c>
-      <c r="M10" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13">
-      <c r="A11" t="s">
-        <v>77</v>
-      </c>
-      <c r="B11">
-        <v>1</v>
-      </c>
-      <c r="C11" t="s">
-        <v>56</v>
-      </c>
-      <c r="D11" s="2" t="s">
+    </row>
+    <row r="28" spans="1:14">
+      <c r="A28" t="s">
+        <v>158</v>
+      </c>
+      <c r="B28" t="s">
+        <v>80</v>
+      </c>
+      <c r="C28" t="s">
+        <v>44</v>
+      </c>
+      <c r="D28" t="s">
+        <v>62</v>
+      </c>
+      <c r="E28" t="s">
+        <v>81</v>
+      </c>
+      <c r="F28" t="s">
+        <v>44</v>
+      </c>
+      <c r="G28" t="s">
+        <v>44</v>
+      </c>
+      <c r="H28" t="s">
+        <v>70</v>
+      </c>
+      <c r="I28" t="s">
+        <v>44</v>
+      </c>
+      <c r="J28" t="s">
+        <v>159</v>
+      </c>
+      <c r="K28" t="s">
+        <v>160</v>
+      </c>
+      <c r="L28" t="s">
+        <v>44</v>
+      </c>
+      <c r="M28" t="s">
         <v>78</v>
       </c>
-      <c r="E11" t="s">
-        <v>42</v>
-      </c>
-      <c r="F11">
-        <v>1</v>
-      </c>
-      <c r="G11" t="s">
-        <v>63</v>
-      </c>
-      <c r="H11" t="s">
-        <v>42</v>
-      </c>
-      <c r="I11" t="s">
-        <v>64</v>
-      </c>
-      <c r="J11" t="s">
-        <v>65</v>
-      </c>
-      <c r="K11" t="s">
-        <v>42</v>
-      </c>
-      <c r="L11" t="s">
-        <v>79</v>
-      </c>
-      <c r="M11" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13">
-      <c r="A12" t="s">
+      <c r="N28" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14">
+      <c r="A29" t="s">
+        <v>161</v>
+      </c>
+      <c r="B29" t="s">
         <v>80</v>
       </c>
-      <c r="B12">
-        <v>1</v>
-      </c>
-      <c r="C12" t="s">
-        <v>56</v>
-      </c>
-      <c r="D12" s="2" t="s">
+      <c r="C29" t="s">
+        <v>44</v>
+      </c>
+      <c r="D29" t="s">
+        <v>62</v>
+      </c>
+      <c r="E29" t="s">
         <v>81</v>
       </c>
-      <c r="E12" t="s">
-        <v>42</v>
-      </c>
-      <c r="F12">
-        <v>1</v>
-      </c>
-      <c r="G12" t="s">
-        <v>63</v>
-      </c>
-      <c r="H12" t="s">
-        <v>42</v>
-      </c>
-      <c r="I12" t="s">
-        <v>64</v>
-      </c>
-      <c r="J12" t="s">
-        <v>65</v>
-      </c>
-      <c r="K12" t="s">
-        <v>42</v>
-      </c>
-      <c r="L12" t="s">
-        <v>82</v>
-      </c>
-      <c r="M12" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13">
-      <c r="A13" t="s">
-        <v>83</v>
-      </c>
-      <c r="B13">
-        <v>1</v>
-      </c>
-      <c r="C13" t="s">
-        <v>56</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="E13" t="s">
-        <v>42</v>
-      </c>
-      <c r="F13">
-        <v>1</v>
-      </c>
-      <c r="G13" t="s">
-        <v>63</v>
-      </c>
-      <c r="H13" t="s">
-        <v>42</v>
-      </c>
-      <c r="I13" t="s">
-        <v>64</v>
-      </c>
-      <c r="J13" t="s">
-        <v>65</v>
-      </c>
-      <c r="K13" t="s">
-        <v>42</v>
-      </c>
-      <c r="L13" t="s">
-        <v>85</v>
-      </c>
-      <c r="M13" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13">
-      <c r="A14" t="s">
+      <c r="F29" t="s">
+        <v>44</v>
+      </c>
+      <c r="G29" t="s">
+        <v>44</v>
+      </c>
+      <c r="H29" t="s">
+        <v>70</v>
+      </c>
+      <c r="I29" t="s">
+        <v>44</v>
+      </c>
+      <c r="J29" t="s">
+        <v>162</v>
+      </c>
+      <c r="K29" t="s">
+        <v>163</v>
+      </c>
+      <c r="L29" t="s">
+        <v>44</v>
+      </c>
+      <c r="M29" t="s">
         <v>86</v>
       </c>
-      <c r="B14">
-        <v>1</v>
-      </c>
-      <c r="C14" t="s">
-        <v>56</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="E14" t="s">
-        <v>42</v>
-      </c>
-      <c r="F14">
-        <v>1</v>
-      </c>
-      <c r="G14" t="s">
-        <v>63</v>
-      </c>
-      <c r="H14" t="s">
-        <v>42</v>
-      </c>
-      <c r="I14" t="s">
-        <v>64</v>
-      </c>
-      <c r="J14" t="s">
-        <v>65</v>
-      </c>
-      <c r="K14" t="s">
-        <v>42</v>
-      </c>
-      <c r="L14" t="s">
-        <v>88</v>
-      </c>
-      <c r="M14" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13">
-      <c r="A15" t="s">
-        <v>89</v>
-      </c>
-      <c r="B15">
-        <v>1</v>
-      </c>
-      <c r="C15" t="s">
-        <v>56</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="E15" t="s">
-        <v>42</v>
-      </c>
-      <c r="F15">
-        <v>1</v>
-      </c>
-      <c r="G15" t="s">
-        <v>63</v>
-      </c>
-      <c r="H15" t="s">
-        <v>42</v>
-      </c>
-      <c r="I15" t="s">
-        <v>64</v>
-      </c>
-      <c r="J15" t="s">
-        <v>65</v>
-      </c>
-      <c r="K15" t="s">
-        <v>42</v>
-      </c>
-      <c r="L15" t="s">
+      <c r="N29" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14">
+      <c r="A30" t="s">
+        <v>164</v>
+      </c>
+      <c r="B30" t="s">
+        <v>80</v>
+      </c>
+      <c r="C30" t="s">
+        <v>165</v>
+      </c>
+      <c r="D30" t="s">
+        <v>62</v>
+      </c>
+      <c r="E30" t="s">
+        <v>81</v>
+      </c>
+      <c r="F30" t="s">
+        <v>44</v>
+      </c>
+      <c r="G30" t="s">
+        <v>44</v>
+      </c>
+      <c r="H30" t="s">
+        <v>70</v>
+      </c>
+      <c r="I30" t="s">
+        <v>44</v>
+      </c>
+      <c r="J30" t="s">
+        <v>166</v>
+      </c>
+      <c r="K30" t="s">
+        <v>167</v>
+      </c>
+      <c r="L30" t="s">
+        <v>44</v>
+      </c>
+      <c r="M30" t="s">
+        <v>168</v>
+      </c>
+      <c r="N30" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14">
+      <c r="A31" t="s">
+        <v>169</v>
+      </c>
+      <c r="B31" t="s">
+        <v>80</v>
+      </c>
+      <c r="C31" t="s">
+        <v>165</v>
+      </c>
+      <c r="D31" t="s">
+        <v>62</v>
+      </c>
+      <c r="E31" t="s">
+        <v>81</v>
+      </c>
+      <c r="F31" t="s">
+        <v>44</v>
+      </c>
+      <c r="G31" t="s">
+        <v>44</v>
+      </c>
+      <c r="H31" t="s">
+        <v>70</v>
+      </c>
+      <c r="I31" t="s">
+        <v>44</v>
+      </c>
+      <c r="J31" t="s">
+        <v>170</v>
+      </c>
+      <c r="K31" t="s">
+        <v>171</v>
+      </c>
+      <c r="L31" t="s">
+        <v>44</v>
+      </c>
+      <c r="M31" t="s">
+        <v>172</v>
+      </c>
+      <c r="N31" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14">
+      <c r="A32" t="s">
+        <v>173</v>
+      </c>
+      <c r="B32" t="s">
+        <v>80</v>
+      </c>
+      <c r="C32" t="s">
+        <v>165</v>
+      </c>
+      <c r="D32" t="s">
+        <v>62</v>
+      </c>
+      <c r="E32" t="s">
+        <v>81</v>
+      </c>
+      <c r="F32" t="s">
+        <v>44</v>
+      </c>
+      <c r="G32" t="s">
+        <v>44</v>
+      </c>
+      <c r="H32" t="s">
+        <v>70</v>
+      </c>
+      <c r="I32" t="s">
+        <v>44</v>
+      </c>
+      <c r="J32" t="s">
+        <v>174</v>
+      </c>
+      <c r="K32" t="s">
+        <v>175</v>
+      </c>
+      <c r="L32" t="s">
+        <v>44</v>
+      </c>
+      <c r="M32" t="s">
+        <v>176</v>
+      </c>
+      <c r="N32" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14">
+      <c r="A33" t="s">
+        <v>177</v>
+      </c>
+      <c r="B33" t="s">
+        <v>80</v>
+      </c>
+      <c r="C33" t="s">
+        <v>165</v>
+      </c>
+      <c r="D33" t="s">
+        <v>62</v>
+      </c>
+      <c r="E33" t="s">
+        <v>81</v>
+      </c>
+      <c r="F33" t="s">
+        <v>44</v>
+      </c>
+      <c r="G33" t="s">
+        <v>44</v>
+      </c>
+      <c r="H33" t="s">
+        <v>70</v>
+      </c>
+      <c r="I33" t="s">
+        <v>44</v>
+      </c>
+      <c r="J33" t="s">
+        <v>178</v>
+      </c>
+      <c r="K33" t="s">
+        <v>179</v>
+      </c>
+      <c r="L33" t="s">
+        <v>44</v>
+      </c>
+      <c r="M33" t="s">
+        <v>180</v>
+      </c>
+      <c r="N33" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14">
+      <c r="A34" t="s">
+        <v>181</v>
+      </c>
+      <c r="B34" t="s">
+        <v>80</v>
+      </c>
+      <c r="C34" t="s">
+        <v>165</v>
+      </c>
+      <c r="D34" t="s">
+        <v>62</v>
+      </c>
+      <c r="E34" t="s">
+        <v>81</v>
+      </c>
+      <c r="F34" t="s">
+        <v>44</v>
+      </c>
+      <c r="G34" t="s">
+        <v>44</v>
+      </c>
+      <c r="H34" t="s">
+        <v>70</v>
+      </c>
+      <c r="I34" t="s">
+        <v>44</v>
+      </c>
+      <c r="J34" t="s">
+        <v>182</v>
+      </c>
+      <c r="K34" t="s">
+        <v>183</v>
+      </c>
+      <c r="L34" t="s">
+        <v>44</v>
+      </c>
+      <c r="M34" t="s">
+        <v>94</v>
+      </c>
+      <c r="N34" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14">
+      <c r="A35" t="s">
+        <v>184</v>
+      </c>
+      <c r="B35" t="s">
+        <v>80</v>
+      </c>
+      <c r="C35" t="s">
+        <v>165</v>
+      </c>
+      <c r="D35" t="s">
+        <v>62</v>
+      </c>
+      <c r="E35" t="s">
+        <v>81</v>
+      </c>
+      <c r="F35" t="s">
+        <v>44</v>
+      </c>
+      <c r="G35" t="s">
+        <v>44</v>
+      </c>
+      <c r="H35" t="s">
+        <v>70</v>
+      </c>
+      <c r="I35" t="s">
+        <v>44</v>
+      </c>
+      <c r="J35" t="s">
+        <v>185</v>
+      </c>
+      <c r="K35" t="s">
+        <v>186</v>
+      </c>
+      <c r="L35" t="s">
+        <v>44</v>
+      </c>
+      <c r="M35" t="s">
+        <v>187</v>
+      </c>
+      <c r="N35" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14">
+      <c r="A36" t="s">
+        <v>188</v>
+      </c>
+      <c r="B36" t="s">
+        <v>80</v>
+      </c>
+      <c r="C36" t="s">
+        <v>165</v>
+      </c>
+      <c r="D36" t="s">
+        <v>62</v>
+      </c>
+      <c r="E36" t="s">
+        <v>81</v>
+      </c>
+      <c r="F36" t="s">
+        <v>44</v>
+      </c>
+      <c r="G36" t="s">
+        <v>44</v>
+      </c>
+      <c r="H36" t="s">
+        <v>107</v>
+      </c>
+      <c r="I36" t="s">
+        <v>44</v>
+      </c>
+      <c r="J36" t="s">
+        <v>189</v>
+      </c>
+      <c r="K36" t="s">
+        <v>190</v>
+      </c>
+      <c r="L36" t="s">
+        <v>44</v>
+      </c>
+      <c r="M36" t="s">
+        <v>191</v>
+      </c>
+      <c r="N36" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14">
+      <c r="A37" t="s">
+        <v>192</v>
+      </c>
+      <c r="B37" t="s">
+        <v>80</v>
+      </c>
+      <c r="C37" t="s">
+        <v>165</v>
+      </c>
+      <c r="D37" t="s">
+        <v>62</v>
+      </c>
+      <c r="E37" t="s">
+        <v>81</v>
+      </c>
+      <c r="F37" t="s">
+        <v>44</v>
+      </c>
+      <c r="G37" t="s">
+        <v>44</v>
+      </c>
+      <c r="H37" t="s">
+        <v>111</v>
+      </c>
+      <c r="I37" t="s">
+        <v>44</v>
+      </c>
+      <c r="J37" t="s">
+        <v>193</v>
+      </c>
+      <c r="K37" t="s">
+        <v>194</v>
+      </c>
+      <c r="L37" t="s">
+        <v>44</v>
+      </c>
+      <c r="M37" t="s">
+        <v>195</v>
+      </c>
+      <c r="N37" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14">
+      <c r="A38" t="s">
+        <v>196</v>
+      </c>
+      <c r="B38" t="s">
+        <v>96</v>
+      </c>
+      <c r="C38" t="s">
+        <v>197</v>
+      </c>
+      <c r="D38" t="s">
+        <v>62</v>
+      </c>
+      <c r="E38" t="s">
+        <v>97</v>
+      </c>
+      <c r="F38" t="s">
+        <v>44</v>
+      </c>
+      <c r="G38" t="s">
+        <v>44</v>
+      </c>
+      <c r="H38" t="s">
+        <v>118</v>
+      </c>
+      <c r="I38" t="s">
+        <v>44</v>
+      </c>
+      <c r="J38" t="s">
+        <v>198</v>
+      </c>
+      <c r="K38" t="s">
+        <v>199</v>
+      </c>
+      <c r="L38" t="s">
+        <v>44</v>
+      </c>
+      <c r="M38" t="s">
+        <v>106</v>
+      </c>
+      <c r="N38" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14">
+      <c r="A39" t="s">
+        <v>200</v>
+      </c>
+      <c r="B39" t="s">
+        <v>92</v>
+      </c>
+      <c r="C39" t="s">
+        <v>197</v>
+      </c>
+      <c r="D39" t="s">
+        <v>62</v>
+      </c>
+      <c r="E39" t="s">
+        <v>93</v>
+      </c>
+      <c r="F39" t="s">
+        <v>44</v>
+      </c>
+      <c r="G39" t="s">
+        <v>44</v>
+      </c>
+      <c r="H39" t="s">
+        <v>123</v>
+      </c>
+      <c r="I39" t="s">
+        <v>44</v>
+      </c>
+      <c r="J39" t="s">
+        <v>201</v>
+      </c>
+      <c r="K39" t="s">
+        <v>202</v>
+      </c>
+      <c r="L39" t="s">
+        <v>44</v>
+      </c>
+      <c r="M39" t="s">
+        <v>203</v>
+      </c>
+      <c r="N39" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14">
+      <c r="A40" t="s">
+        <v>204</v>
+      </c>
+      <c r="B40" t="s">
+        <v>80</v>
+      </c>
+      <c r="C40" t="s">
+        <v>44</v>
+      </c>
+      <c r="D40" t="s">
+        <v>62</v>
+      </c>
+      <c r="E40" t="s">
+        <v>81</v>
+      </c>
+      <c r="F40" t="s">
+        <v>44</v>
+      </c>
+      <c r="G40" t="s">
+        <v>44</v>
+      </c>
+      <c r="H40" t="s">
+        <v>128</v>
+      </c>
+      <c r="I40" t="s">
+        <v>44</v>
+      </c>
+      <c r="J40" t="s">
+        <v>51</v>
+      </c>
+      <c r="K40" t="s">
+        <v>205</v>
+      </c>
+      <c r="L40" t="s">
+        <v>50</v>
+      </c>
+      <c r="M40" t="s">
+        <v>51</v>
+      </c>
+      <c r="N40" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14">
+      <c r="A41" t="s">
+        <v>206</v>
+      </c>
+      <c r="B41" t="s">
+        <v>207</v>
+      </c>
+      <c r="C41" t="s">
+        <v>44</v>
+      </c>
+      <c r="D41" t="s">
+        <v>117</v>
+      </c>
+      <c r="E41" t="s">
+        <v>81</v>
+      </c>
+      <c r="F41" t="s">
+        <v>44</v>
+      </c>
+      <c r="G41" t="s">
+        <v>44</v>
+      </c>
+      <c r="H41" t="s">
+        <v>133</v>
+      </c>
+      <c r="I41" t="s">
+        <v>44</v>
+      </c>
+      <c r="J41" t="s">
+        <v>51</v>
+      </c>
+      <c r="K41" t="s">
+        <v>208</v>
+      </c>
+      <c r="L41" t="s">
+        <v>50</v>
+      </c>
+      <c r="M41" t="s">
+        <v>51</v>
+      </c>
+      <c r="N41" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14">
+      <c r="A42" t="s">
+        <v>209</v>
+      </c>
+      <c r="B42" t="s">
+        <v>147</v>
+      </c>
+      <c r="C42" t="s">
+        <v>165</v>
+      </c>
+      <c r="D42" t="s">
+        <v>45</v>
+      </c>
+      <c r="E42" t="s">
+        <v>81</v>
+      </c>
+      <c r="F42" t="s">
+        <v>44</v>
+      </c>
+      <c r="G42" t="s">
+        <v>44</v>
+      </c>
+      <c r="H42" t="s">
+        <v>138</v>
+      </c>
+      <c r="I42" t="s">
+        <v>44</v>
+      </c>
+      <c r="J42" t="s">
+        <v>51</v>
+      </c>
+      <c r="K42" t="s">
+        <v>210</v>
+      </c>
+      <c r="L42" t="s">
+        <v>50</v>
+      </c>
+      <c r="M42" t="s">
+        <v>51</v>
+      </c>
+      <c r="N42" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14">
+      <c r="A43" t="s">
+        <v>211</v>
+      </c>
+      <c r="B43" t="s">
+        <v>150</v>
+      </c>
+      <c r="C43" t="s">
+        <v>165</v>
+      </c>
+      <c r="D43" t="s">
+        <v>55</v>
+      </c>
+      <c r="E43" t="s">
+        <v>81</v>
+      </c>
+      <c r="F43" t="s">
+        <v>44</v>
+      </c>
+      <c r="G43" t="s">
+        <v>44</v>
+      </c>
+      <c r="H43" t="s">
+        <v>143</v>
+      </c>
+      <c r="I43" t="s">
+        <v>44</v>
+      </c>
+      <c r="J43" t="s">
+        <v>51</v>
+      </c>
+      <c r="K43" t="s">
+        <v>212</v>
+      </c>
+      <c r="L43" t="s">
+        <v>50</v>
+      </c>
+      <c r="M43" t="s">
+        <v>51</v>
+      </c>
+      <c r="N43" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14">
+      <c r="A44" t="s">
+        <v>213</v>
+      </c>
+      <c r="B44" t="s">
+        <v>80</v>
+      </c>
+      <c r="C44" t="s">
+        <v>165</v>
+      </c>
+      <c r="D44" t="s">
+        <v>62</v>
+      </c>
+      <c r="E44" t="s">
+        <v>81</v>
+      </c>
+      <c r="F44" t="s">
+        <v>44</v>
+      </c>
+      <c r="G44" t="s">
+        <v>44</v>
+      </c>
+      <c r="H44" t="s">
+        <v>128</v>
+      </c>
+      <c r="I44" t="s">
+        <v>44</v>
+      </c>
+      <c r="J44" t="s">
+        <v>51</v>
+      </c>
+      <c r="K44" t="s">
+        <v>214</v>
+      </c>
+      <c r="L44" t="s">
+        <v>50</v>
+      </c>
+      <c r="M44" t="s">
+        <v>51</v>
+      </c>
+      <c r="N44" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14">
+      <c r="A45" t="s">
+        <v>215</v>
+      </c>
+      <c r="B45" t="s">
+        <v>207</v>
+      </c>
+      <c r="C45" t="s">
+        <v>165</v>
+      </c>
+      <c r="D45" t="s">
+        <v>117</v>
+      </c>
+      <c r="E45" t="s">
+        <v>81</v>
+      </c>
+      <c r="F45" t="s">
+        <v>44</v>
+      </c>
+      <c r="G45" t="s">
+        <v>44</v>
+      </c>
+      <c r="H45" t="s">
+        <v>143</v>
+      </c>
+      <c r="I45" t="s">
+        <v>44</v>
+      </c>
+      <c r="J45" t="s">
+        <v>51</v>
+      </c>
+      <c r="K45" t="s">
+        <v>216</v>
+      </c>
+      <c r="L45" t="s">
+        <v>50</v>
+      </c>
+      <c r="M45" t="s">
+        <v>51</v>
+      </c>
+      <c r="N45" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14">
+      <c r="A46" t="s">
+        <v>217</v>
+      </c>
+      <c r="B46" t="s">
+        <v>218</v>
+      </c>
+      <c r="C46" t="s">
+        <v>197</v>
+      </c>
+      <c r="D46" t="s">
+        <v>45</v>
+      </c>
+      <c r="E46" t="s">
+        <v>97</v>
+      </c>
+      <c r="F46" t="s">
+        <v>44</v>
+      </c>
+      <c r="G46" t="s">
+        <v>44</v>
+      </c>
+      <c r="H46" t="s">
+        <v>143</v>
+      </c>
+      <c r="I46" t="s">
+        <v>44</v>
+      </c>
+      <c r="J46" t="s">
+        <v>51</v>
+      </c>
+      <c r="K46" t="s">
+        <v>219</v>
+      </c>
+      <c r="L46" t="s">
+        <v>50</v>
+      </c>
+      <c r="M46" t="s">
+        <v>51</v>
+      </c>
+      <c r="N46" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14">
+      <c r="A47" t="s">
+        <v>141</v>
+      </c>
+      <c r="B47" t="s">
+        <v>142</v>
+      </c>
+      <c r="C47" t="s">
+        <v>197</v>
+      </c>
+      <c r="D47" t="s">
+        <v>55</v>
+      </c>
+      <c r="E47" t="s">
+        <v>97</v>
+      </c>
+      <c r="F47" t="s">
+        <v>44</v>
+      </c>
+      <c r="G47" t="s">
+        <v>44</v>
+      </c>
+      <c r="H47" t="s">
+        <v>143</v>
+      </c>
+      <c r="I47" t="s">
+        <v>44</v>
+      </c>
+      <c r="J47" t="s">
+        <v>51</v>
+      </c>
+      <c r="K47" t="s">
+        <v>145</v>
+      </c>
+      <c r="L47" t="s">
+        <v>50</v>
+      </c>
+      <c r="M47" t="s">
+        <v>51</v>
+      </c>
+      <c r="N47" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14">
+      <c r="A48" t="s">
+        <v>95</v>
+      </c>
+      <c r="B48" t="s">
+        <v>96</v>
+      </c>
+      <c r="C48" t="s">
+        <v>197</v>
+      </c>
+      <c r="D48" t="s">
+        <v>62</v>
+      </c>
+      <c r="E48" t="s">
+        <v>97</v>
+      </c>
+      <c r="F48" t="s">
+        <v>44</v>
+      </c>
+      <c r="G48" t="s">
+        <v>44</v>
+      </c>
+      <c r="H48" t="s">
+        <v>143</v>
+      </c>
+      <c r="I48" t="s">
+        <v>44</v>
+      </c>
+      <c r="J48" t="s">
+        <v>51</v>
+      </c>
+      <c r="K48" t="s">
+        <v>220</v>
+      </c>
+      <c r="L48" t="s">
+        <v>50</v>
+      </c>
+      <c r="M48" t="s">
+        <v>51</v>
+      </c>
+      <c r="N48" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14">
+      <c r="A49" t="s">
+        <v>221</v>
+      </c>
+      <c r="B49" t="s">
+        <v>222</v>
+      </c>
+      <c r="C49" t="s">
+        <v>197</v>
+      </c>
+      <c r="D49" t="s">
+        <v>117</v>
+      </c>
+      <c r="E49" t="s">
+        <v>97</v>
+      </c>
+      <c r="F49" t="s">
+        <v>44</v>
+      </c>
+      <c r="G49" t="s">
+        <v>44</v>
+      </c>
+      <c r="H49" t="s">
+        <v>143</v>
+      </c>
+      <c r="I49" t="s">
+        <v>44</v>
+      </c>
+      <c r="J49" t="s">
+        <v>51</v>
+      </c>
+      <c r="K49" t="s">
+        <v>223</v>
+      </c>
+      <c r="L49" t="s">
+        <v>50</v>
+      </c>
+      <c r="M49" t="s">
+        <v>51</v>
+      </c>
+      <c r="N49" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14">
+      <c r="A50" t="s">
+        <v>136</v>
+      </c>
+      <c r="B50" t="s">
+        <v>137</v>
+      </c>
+      <c r="C50" t="s">
+        <v>197</v>
+      </c>
+      <c r="D50" t="s">
+        <v>45</v>
+      </c>
+      <c r="E50" t="s">
+        <v>93</v>
+      </c>
+      <c r="F50" t="s">
+        <v>44</v>
+      </c>
+      <c r="G50" t="s">
+        <v>44</v>
+      </c>
+      <c r="H50" t="s">
+        <v>143</v>
+      </c>
+      <c r="I50" t="s">
+        <v>44</v>
+      </c>
+      <c r="J50" t="s">
+        <v>51</v>
+      </c>
+      <c r="K50" t="s">
+        <v>140</v>
+      </c>
+      <c r="L50" t="s">
+        <v>50</v>
+      </c>
+      <c r="M50" t="s">
+        <v>51</v>
+      </c>
+      <c r="N50" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14">
+      <c r="A51" t="s">
+        <v>224</v>
+      </c>
+      <c r="B51" t="s">
+        <v>225</v>
+      </c>
+      <c r="C51" t="s">
+        <v>197</v>
+      </c>
+      <c r="D51" t="s">
+        <v>55</v>
+      </c>
+      <c r="E51" t="s">
+        <v>93</v>
+      </c>
+      <c r="F51" t="s">
+        <v>44</v>
+      </c>
+      <c r="G51" t="s">
+        <v>44</v>
+      </c>
+      <c r="H51" t="s">
+        <v>143</v>
+      </c>
+      <c r="I51" t="s">
+        <v>44</v>
+      </c>
+      <c r="J51" t="s">
+        <v>51</v>
+      </c>
+      <c r="K51" t="s">
+        <v>226</v>
+      </c>
+      <c r="L51" t="s">
+        <v>50</v>
+      </c>
+      <c r="M51" t="s">
+        <v>51</v>
+      </c>
+      <c r="N51" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14">
+      <c r="A52" t="s">
         <v>91</v>
       </c>
-      <c r="M15" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13">
-      <c r="A16" t="s">
-        <v>55</v>
-      </c>
-      <c r="B16">
-        <v>1</v>
-      </c>
-      <c r="C16" t="s">
-        <v>56</v>
-      </c>
-      <c r="D16" t="s">
-        <v>41</v>
-      </c>
-      <c r="E16" t="s">
-        <v>42</v>
-      </c>
-      <c r="F16">
-        <v>1</v>
-      </c>
-      <c r="G16" t="s">
+      <c r="B52" t="s">
         <v>92</v>
       </c>
-      <c r="H16" t="s">
-        <v>42</v>
-      </c>
-      <c r="I16" t="s">
+      <c r="C52" t="s">
+        <v>197</v>
+      </c>
+      <c r="D52" t="s">
+        <v>62</v>
+      </c>
+      <c r="E52" t="s">
         <v>93</v>
       </c>
-      <c r="J16" t="s">
-        <v>94</v>
-      </c>
-      <c r="K16" t="s">
-        <v>46</v>
-      </c>
-      <c r="L16" t="s">
-        <v>95</v>
-      </c>
-      <c r="M16" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13">
-      <c r="A17" t="s">
-        <v>68</v>
-      </c>
-      <c r="B17">
-        <v>1</v>
-      </c>
-      <c r="C17" t="s">
-        <v>56</v>
-      </c>
-      <c r="D17" t="s">
-        <v>69</v>
-      </c>
-      <c r="E17" t="s">
-        <v>42</v>
-      </c>
-      <c r="F17">
-        <v>1</v>
-      </c>
-      <c r="G17" t="s">
-        <v>96</v>
-      </c>
-      <c r="H17" t="s">
-        <v>42</v>
-      </c>
-      <c r="I17" t="s">
-        <v>97</v>
-      </c>
-      <c r="J17" t="s">
-        <v>98</v>
-      </c>
-      <c r="K17" t="s">
-        <v>46</v>
-      </c>
-      <c r="L17" t="s">
-        <v>99</v>
-      </c>
-      <c r="M17" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13">
-      <c r="A18" t="s">
-        <v>100</v>
-      </c>
-      <c r="B18">
-        <v>1</v>
-      </c>
-      <c r="C18" t="s">
-        <v>101</v>
-      </c>
-      <c r="D18" t="s">
-        <v>62</v>
-      </c>
-      <c r="E18" t="s">
-        <v>42</v>
-      </c>
-      <c r="F18">
-        <v>1</v>
-      </c>
-      <c r="G18" t="s">
-        <v>102</v>
-      </c>
-      <c r="H18" t="s">
-        <v>42</v>
-      </c>
-      <c r="I18" t="s">
-        <v>103</v>
-      </c>
-      <c r="J18" t="s">
-        <v>104</v>
-      </c>
-      <c r="K18" t="s">
-        <v>46</v>
-      </c>
-      <c r="L18" t="s">
-        <v>47</v>
-      </c>
-      <c r="M18" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13">
-      <c r="A19" t="s">
-        <v>105</v>
-      </c>
-      <c r="B19">
-        <v>1</v>
-      </c>
-      <c r="C19" t="s">
-        <v>40</v>
-      </c>
-      <c r="D19" t="s">
-        <v>69</v>
-      </c>
-      <c r="E19" t="s">
-        <v>42</v>
-      </c>
-      <c r="F19">
-        <v>1</v>
-      </c>
-      <c r="G19" t="s">
-        <v>106</v>
-      </c>
-      <c r="H19" t="s">
-        <v>42</v>
-      </c>
-      <c r="I19" t="s">
-        <v>107</v>
-      </c>
-      <c r="J19" t="s">
-        <v>108</v>
-      </c>
-      <c r="K19" t="s">
-        <v>46</v>
-      </c>
-      <c r="L19" t="s">
-        <v>47</v>
-      </c>
-      <c r="M19" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13">
-      <c r="A20" t="s">
-        <v>109</v>
-      </c>
-      <c r="B20">
-        <v>1</v>
-      </c>
-      <c r="C20" t="s">
+      <c r="F52" t="s">
+        <v>44</v>
+      </c>
+      <c r="G52" t="s">
+        <v>44</v>
+      </c>
+      <c r="H52" t="s">
+        <v>143</v>
+      </c>
+      <c r="I52" t="s">
+        <v>44</v>
+      </c>
+      <c r="J52" t="s">
+        <v>51</v>
+      </c>
+      <c r="K52" t="s">
+        <v>227</v>
+      </c>
+      <c r="L52" t="s">
         <v>50</v>
       </c>
-      <c r="D20" t="s">
-        <v>69</v>
-      </c>
-      <c r="E20" t="s">
-        <v>42</v>
-      </c>
-      <c r="F20">
-        <v>1</v>
-      </c>
-      <c r="G20" t="s">
-        <v>110</v>
-      </c>
-      <c r="H20" t="s">
-        <v>42</v>
-      </c>
-      <c r="I20" t="s">
-        <v>111</v>
-      </c>
-      <c r="J20" t="s">
-        <v>112</v>
-      </c>
-      <c r="K20" t="s">
-        <v>46</v>
-      </c>
-      <c r="L20" t="s">
-        <v>47</v>
-      </c>
-      <c r="M20" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13">
-      <c r="A21" t="s">
-        <v>113</v>
-      </c>
-      <c r="B21">
-        <v>1</v>
-      </c>
-      <c r="C21" t="s">
-        <v>101</v>
-      </c>
-      <c r="D21" t="s">
-        <v>75</v>
-      </c>
-      <c r="E21" t="s">
-        <v>42</v>
-      </c>
-      <c r="F21">
-        <v>1</v>
-      </c>
-      <c r="G21" t="s">
-        <v>114</v>
-      </c>
-      <c r="H21" t="s">
-        <v>42</v>
-      </c>
-      <c r="I21" t="s">
-        <v>115</v>
-      </c>
-      <c r="J21" t="s">
-        <v>116</v>
-      </c>
-      <c r="K21" t="s">
-        <v>46</v>
-      </c>
-      <c r="L21" t="s">
-        <v>47</v>
-      </c>
-      <c r="M21" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13">
-      <c r="A22" t="s">
+      <c r="M52" t="s">
+        <v>51</v>
+      </c>
+      <c r="N52" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14">
+      <c r="A53" t="s">
+        <v>228</v>
+      </c>
+      <c r="B53" t="s">
+        <v>229</v>
+      </c>
+      <c r="C53" t="s">
+        <v>197</v>
+      </c>
+      <c r="D53" t="s">
         <v>117</v>
       </c>
-      <c r="B22">
-        <v>1</v>
-      </c>
-      <c r="C22" t="s">
-        <v>40</v>
-      </c>
-      <c r="D22" t="s">
-        <v>81</v>
-      </c>
-      <c r="E22" t="s">
-        <v>42</v>
-      </c>
-      <c r="F22">
-        <v>1</v>
-      </c>
-      <c r="G22" t="s">
-        <v>118</v>
-      </c>
-      <c r="H22" t="s">
-        <v>42</v>
-      </c>
-      <c r="I22" t="s">
-        <v>119</v>
-      </c>
-      <c r="J22" t="s">
-        <v>120</v>
-      </c>
-      <c r="K22" t="s">
-        <v>46</v>
-      </c>
-      <c r="L22" t="s">
-        <v>47</v>
-      </c>
-      <c r="M22" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13">
-      <c r="A23" t="s">
-        <v>121</v>
-      </c>
-      <c r="B23">
-        <v>1</v>
-      </c>
-      <c r="C23" t="s">
+      <c r="E53" t="s">
+        <v>93</v>
+      </c>
+      <c r="F53" t="s">
+        <v>44</v>
+      </c>
+      <c r="G53" t="s">
+        <v>44</v>
+      </c>
+      <c r="H53" t="s">
+        <v>143</v>
+      </c>
+      <c r="I53" t="s">
+        <v>44</v>
+      </c>
+      <c r="J53" t="s">
+        <v>51</v>
+      </c>
+      <c r="K53" t="s">
+        <v>230</v>
+      </c>
+      <c r="L53" t="s">
         <v>50</v>
       </c>
-      <c r="D23" t="s">
-        <v>84</v>
-      </c>
-      <c r="E23" t="s">
-        <v>42</v>
-      </c>
-      <c r="F23">
-        <v>1</v>
-      </c>
-      <c r="G23" t="s">
-        <v>122</v>
-      </c>
-      <c r="H23" t="s">
-        <v>42</v>
-      </c>
-      <c r="I23" t="s">
-        <v>123</v>
-      </c>
-      <c r="J23" t="s">
-        <v>124</v>
-      </c>
-      <c r="K23" t="s">
-        <v>46</v>
-      </c>
-      <c r="L23" t="s">
-        <v>47</v>
-      </c>
-      <c r="M23" t="s">
-        <v>67</v>
+      <c r="M53" t="s">
+        <v>51</v>
+      </c>
+      <c r="N53" t="s">
+        <v>74</v>
       </c>
     </row>
   </sheetData>

--- a/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/制造_躯体材料配置表_Manufacture_BodyPartConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/制造_躯体材料配置表_Manufacture_BodyPartConfig.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="742" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="816" uniqueCount="237">
   <si>
     <t>躯体ID</t>
   </si>
@@ -472,66 +472,96 @@
     <t>Art_BP_Torso_Angel</t>
   </si>
   <si>
+    <t>BP_Head_Undead_0</t>
+  </si>
+  <si>
+    <t>亡灵头部</t>
+  </si>
+  <si>
+    <t>Art_BP_Head_Undead_1</t>
+  </si>
+  <si>
+    <t>BP_Torso_Undead_0</t>
+  </si>
+  <si>
+    <t>亡灵躯干</t>
+  </si>
+  <si>
+    <t>Art_BP_Torso_Undead_1</t>
+  </si>
+  <si>
+    <t>BP_Arm_Undead_Warrior_0</t>
+  </si>
+  <si>
+    <t>战士</t>
+  </si>
+  <si>
+    <t>Art_BP_Arm_Undead_Warrior</t>
+  </si>
+  <si>
+    <t>BP_Arm_Undead_Archer_0</t>
+  </si>
+  <si>
+    <t>射手</t>
+  </si>
+  <si>
+    <t>Art_BP_Arm_Undead_Archer</t>
+  </si>
+  <si>
+    <t>BP_Arm_Undead_Mage_0</t>
+  </si>
+  <si>
+    <t>法师</t>
+  </si>
+  <si>
+    <t>Art_BP_Arm_Undead_Mage</t>
+  </si>
+  <si>
+    <t>BP_Arm_Undead_Rogue_0</t>
+  </si>
+  <si>
+    <t>盗贼</t>
+  </si>
+  <si>
+    <t>Art_BP_Arm_Undead_Rogue</t>
+  </si>
+  <si>
+    <t>BP_Arm_Undead_0</t>
+  </si>
+  <si>
+    <t>Art_BP_Arm_Undead_1</t>
+  </si>
+  <si>
+    <t>BP_Leg_Undead_0</t>
+  </si>
+  <si>
+    <t>亡灵腿部</t>
+  </si>
+  <si>
+    <t>Art_BP_Leg_Undead_1</t>
+  </si>
+  <si>
     <t>BP_Head_Undead_1</t>
   </si>
   <si>
-    <t>亡灵头部</t>
-  </si>
-  <si>
-    <t>Art_BP_Head_Undead_1</t>
-  </si>
-  <si>
     <t>BP_Torso_Undead_1</t>
   </si>
   <si>
-    <t>亡灵躯干</t>
-  </si>
-  <si>
-    <t>Art_BP_Torso_Undead_1</t>
-  </si>
-  <si>
     <t>BP_Arm_Undead_Warrior</t>
   </si>
   <si>
-    <t>战士</t>
-  </si>
-  <si>
-    <t>Art_BP_Arm_Undead_Warrior</t>
-  </si>
-  <si>
     <t>BP_Arm_Undead_Archer</t>
   </si>
   <si>
-    <t>射手</t>
-  </si>
-  <si>
-    <t>Art_BP_Arm_Undead_Archer</t>
-  </si>
-  <si>
     <t>BP_Arm_Undead_Mage</t>
   </si>
   <si>
-    <t>法师</t>
-  </si>
-  <si>
-    <t>Art_BP_Arm_Undead_Mage</t>
-  </si>
-  <si>
     <t>BP_Arm_Undead_Rogue</t>
   </si>
   <si>
-    <t>盗贼</t>
-  </si>
-  <si>
-    <t>Art_BP_Arm_Undead_Rogue</t>
-  </si>
-  <si>
     <t>BP_Arm_Undead_Guardian</t>
   </si>
   <si>
-    <t>2</t>
-  </si>
-  <si>
     <t>近卫</t>
   </si>
   <si>
@@ -625,9 +655,6 @@
     <t>BP_Arm_Angel_Paladin</t>
   </si>
   <si>
-    <t>3</t>
-  </si>
-  <si>
     <t>圣骑士</t>
   </si>
   <si>
@@ -649,16 +676,7 @@
     <t>BP_Arm_Undead_1</t>
   </si>
   <si>
-    <t>Art_BP_Arm_Undead_1</t>
-  </si>
-  <si>
     <t>BP_Leg_Undead_1</t>
-  </si>
-  <si>
-    <t>亡灵腿部</t>
-  </si>
-  <si>
-    <t>Art_BP_Leg_Undead_1</t>
   </si>
   <si>
     <t>BP_Head_Undead_2</t>
@@ -737,14 +755,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1212,148 +1223,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1707,8 +1718,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N53"/>
+  <dimension ref="A1:N61"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <cols>
+    <col min="1" max="1" width="24.625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:14">
       <c r="A1" t="s">
@@ -2729,8 +2743,8 @@
       <c r="B24" t="s">
         <v>147</v>
       </c>
-      <c r="C24" t="s">
-        <v>44</v>
+      <c r="C24">
+        <v>1</v>
       </c>
       <c r="D24" t="s">
         <v>45</v>
@@ -2773,8 +2787,8 @@
       <c r="B25" t="s">
         <v>150</v>
       </c>
-      <c r="C25" t="s">
-        <v>44</v>
+      <c r="C25">
+        <v>1</v>
       </c>
       <c r="D25" t="s">
         <v>55</v>
@@ -2817,8 +2831,8 @@
       <c r="B26" t="s">
         <v>80</v>
       </c>
-      <c r="C26" t="s">
-        <v>44</v>
+      <c r="C26">
+        <v>1</v>
       </c>
       <c r="D26" t="s">
         <v>62</v>
@@ -2861,8 +2875,8 @@
       <c r="B27" t="s">
         <v>80</v>
       </c>
-      <c r="C27" t="s">
-        <v>44</v>
+      <c r="C27">
+        <v>1</v>
       </c>
       <c r="D27" t="s">
         <v>62</v>
@@ -2905,8 +2919,8 @@
       <c r="B28" t="s">
         <v>80</v>
       </c>
-      <c r="C28" t="s">
-        <v>44</v>
+      <c r="C28">
+        <v>1</v>
       </c>
       <c r="D28" t="s">
         <v>62</v>
@@ -2949,8 +2963,8 @@
       <c r="B29" t="s">
         <v>80</v>
       </c>
-      <c r="C29" t="s">
-        <v>44</v>
+      <c r="C29">
+        <v>1</v>
       </c>
       <c r="D29" t="s">
         <v>62</v>
@@ -2993,8 +3007,8 @@
       <c r="B30" t="s">
         <v>80</v>
       </c>
-      <c r="C30" t="s">
-        <v>165</v>
+      <c r="C30">
+        <v>1</v>
       </c>
       <c r="D30" t="s">
         <v>62</v>
@@ -3009,39 +3023,39 @@
         <v>44</v>
       </c>
       <c r="H30" t="s">
-        <v>70</v>
+        <v>128</v>
       </c>
       <c r="I30" t="s">
         <v>44</v>
       </c>
       <c r="J30" t="s">
-        <v>166</v>
+        <v>51</v>
       </c>
       <c r="K30" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="L30" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="M30" t="s">
-        <v>168</v>
+        <v>51</v>
       </c>
       <c r="N30" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B31" t="s">
-        <v>80</v>
-      </c>
-      <c r="C31" t="s">
-        <v>165</v>
+        <v>167</v>
+      </c>
+      <c r="C31">
+        <v>1</v>
       </c>
       <c r="D31" t="s">
-        <v>62</v>
+        <v>117</v>
       </c>
       <c r="E31" t="s">
         <v>81</v>
@@ -3053,39 +3067,39 @@
         <v>44</v>
       </c>
       <c r="H31" t="s">
-        <v>70</v>
+        <v>133</v>
       </c>
       <c r="I31" t="s">
         <v>44</v>
       </c>
       <c r="J31" t="s">
-        <v>170</v>
+        <v>51</v>
       </c>
       <c r="K31" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="L31" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="M31" t="s">
-        <v>172</v>
+        <v>51</v>
       </c>
       <c r="N31" t="s">
-        <v>74</v>
+        <v>59</v>
       </c>
     </row>
     <row r="32" spans="1:14">
       <c r="A32" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="B32" t="s">
-        <v>80</v>
-      </c>
-      <c r="C32" t="s">
-        <v>165</v>
+        <v>147</v>
+      </c>
+      <c r="C32">
+        <v>2</v>
       </c>
       <c r="D32" t="s">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="E32" t="s">
         <v>81</v>
@@ -3097,22 +3111,22 @@
         <v>44</v>
       </c>
       <c r="H32" t="s">
-        <v>70</v>
+        <v>47</v>
       </c>
       <c r="I32" t="s">
         <v>44</v>
       </c>
       <c r="J32" t="s">
-        <v>174</v>
+        <v>51</v>
       </c>
       <c r="K32" t="s">
-        <v>175</v>
+        <v>148</v>
       </c>
       <c r="L32" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="M32" t="s">
-        <v>176</v>
+        <v>51</v>
       </c>
       <c r="N32" t="s">
         <v>52</v>
@@ -3120,16 +3134,16 @@
     </row>
     <row r="33" spans="1:14">
       <c r="A33" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="B33" t="s">
-        <v>80</v>
-      </c>
-      <c r="C33" t="s">
-        <v>165</v>
+        <v>150</v>
+      </c>
+      <c r="C33">
+        <v>2</v>
       </c>
       <c r="D33" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="E33" t="s">
         <v>81</v>
@@ -3141,22 +3155,22 @@
         <v>44</v>
       </c>
       <c r="H33" t="s">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="I33" t="s">
         <v>44</v>
       </c>
       <c r="J33" t="s">
-        <v>178</v>
+        <v>51</v>
       </c>
       <c r="K33" t="s">
-        <v>179</v>
+        <v>151</v>
       </c>
       <c r="L33" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="M33" t="s">
-        <v>180</v>
+        <v>51</v>
       </c>
       <c r="N33" t="s">
         <v>59</v>
@@ -3164,13 +3178,13 @@
     </row>
     <row r="34" spans="1:14">
       <c r="A34" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="B34" t="s">
         <v>80</v>
       </c>
-      <c r="C34" t="s">
-        <v>165</v>
+      <c r="C34">
+        <v>2</v>
       </c>
       <c r="D34" t="s">
         <v>62</v>
@@ -3185,22 +3199,22 @@
         <v>44</v>
       </c>
       <c r="H34" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="I34" t="s">
         <v>44</v>
       </c>
       <c r="J34" t="s">
-        <v>182</v>
+        <v>153</v>
       </c>
       <c r="K34" t="s">
-        <v>183</v>
+        <v>154</v>
       </c>
       <c r="L34" t="s">
         <v>44</v>
       </c>
       <c r="M34" t="s">
-        <v>94</v>
+        <v>66</v>
       </c>
       <c r="N34" t="s">
         <v>59</v>
@@ -3208,13 +3222,13 @@
     </row>
     <row r="35" spans="1:14">
       <c r="A35" t="s">
-        <v>184</v>
+        <v>172</v>
       </c>
       <c r="B35" t="s">
         <v>80</v>
       </c>
-      <c r="C35" t="s">
-        <v>165</v>
+      <c r="C35">
+        <v>2</v>
       </c>
       <c r="D35" t="s">
         <v>62</v>
@@ -3235,16 +3249,16 @@
         <v>44</v>
       </c>
       <c r="J35" t="s">
-        <v>185</v>
+        <v>156</v>
       </c>
       <c r="K35" t="s">
-        <v>186</v>
+        <v>157</v>
       </c>
       <c r="L35" t="s">
         <v>44</v>
       </c>
       <c r="M35" t="s">
-        <v>187</v>
+        <v>73</v>
       </c>
       <c r="N35" t="s">
         <v>74</v>
@@ -3252,13 +3266,13 @@
     </row>
     <row r="36" spans="1:14">
       <c r="A36" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="B36" t="s">
         <v>80</v>
       </c>
-      <c r="C36" t="s">
-        <v>165</v>
+      <c r="C36">
+        <v>2</v>
       </c>
       <c r="D36" t="s">
         <v>62</v>
@@ -3273,22 +3287,22 @@
         <v>44</v>
       </c>
       <c r="H36" t="s">
-        <v>107</v>
+        <v>70</v>
       </c>
       <c r="I36" t="s">
         <v>44</v>
       </c>
       <c r="J36" t="s">
-        <v>189</v>
+        <v>159</v>
       </c>
       <c r="K36" t="s">
-        <v>190</v>
+        <v>160</v>
       </c>
       <c r="L36" t="s">
         <v>44</v>
       </c>
       <c r="M36" t="s">
-        <v>191</v>
+        <v>78</v>
       </c>
       <c r="N36" t="s">
         <v>52</v>
@@ -3296,13 +3310,13 @@
     </row>
     <row r="37" spans="1:14">
       <c r="A37" t="s">
-        <v>192</v>
+        <v>174</v>
       </c>
       <c r="B37" t="s">
         <v>80</v>
       </c>
-      <c r="C37" t="s">
-        <v>165</v>
+      <c r="C37">
+        <v>2</v>
       </c>
       <c r="D37" t="s">
         <v>62</v>
@@ -3317,42 +3331,42 @@
         <v>44</v>
       </c>
       <c r="H37" t="s">
-        <v>111</v>
+        <v>70</v>
       </c>
       <c r="I37" t="s">
         <v>44</v>
       </c>
       <c r="J37" t="s">
-        <v>193</v>
+        <v>162</v>
       </c>
       <c r="K37" t="s">
-        <v>194</v>
+        <v>163</v>
       </c>
       <c r="L37" t="s">
         <v>44</v>
       </c>
       <c r="M37" t="s">
-        <v>195</v>
+        <v>86</v>
       </c>
       <c r="N37" t="s">
-        <v>52</v>
+        <v>74</v>
       </c>
     </row>
     <row r="38" spans="1:14">
       <c r="A38" t="s">
-        <v>196</v>
+        <v>175</v>
       </c>
       <c r="B38" t="s">
-        <v>96</v>
-      </c>
-      <c r="C38" t="s">
-        <v>197</v>
+        <v>80</v>
+      </c>
+      <c r="C38">
+        <v>3</v>
       </c>
       <c r="D38" t="s">
         <v>62</v>
       </c>
       <c r="E38" t="s">
-        <v>97</v>
+        <v>81</v>
       </c>
       <c r="F38" t="s">
         <v>44</v>
@@ -3361,22 +3375,22 @@
         <v>44</v>
       </c>
       <c r="H38" t="s">
-        <v>118</v>
+        <v>70</v>
       </c>
       <c r="I38" t="s">
         <v>44</v>
       </c>
       <c r="J38" t="s">
-        <v>198</v>
+        <v>176</v>
       </c>
       <c r="K38" t="s">
-        <v>199</v>
+        <v>177</v>
       </c>
       <c r="L38" t="s">
         <v>44</v>
       </c>
       <c r="M38" t="s">
-        <v>106</v>
+        <v>178</v>
       </c>
       <c r="N38" t="s">
         <v>59</v>
@@ -3384,19 +3398,19 @@
     </row>
     <row r="39" spans="1:14">
       <c r="A39" t="s">
-        <v>200</v>
+        <v>179</v>
       </c>
       <c r="B39" t="s">
-        <v>92</v>
-      </c>
-      <c r="C39" t="s">
-        <v>197</v>
+        <v>80</v>
+      </c>
+      <c r="C39">
+        <v>3</v>
       </c>
       <c r="D39" t="s">
         <v>62</v>
       </c>
       <c r="E39" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="F39" t="s">
         <v>44</v>
@@ -3405,36 +3419,36 @@
         <v>44</v>
       </c>
       <c r="H39" t="s">
-        <v>123</v>
+        <v>70</v>
       </c>
       <c r="I39" t="s">
         <v>44</v>
       </c>
       <c r="J39" t="s">
-        <v>201</v>
+        <v>180</v>
       </c>
       <c r="K39" t="s">
-        <v>202</v>
+        <v>181</v>
       </c>
       <c r="L39" t="s">
         <v>44</v>
       </c>
       <c r="M39" t="s">
-        <v>203</v>
+        <v>182</v>
       </c>
       <c r="N39" t="s">
-        <v>52</v>
+        <v>74</v>
       </c>
     </row>
     <row r="40" spans="1:14">
       <c r="A40" t="s">
-        <v>204</v>
+        <v>183</v>
       </c>
       <c r="B40" t="s">
         <v>80</v>
       </c>
-      <c r="C40" t="s">
-        <v>44</v>
+      <c r="C40">
+        <v>3</v>
       </c>
       <c r="D40" t="s">
         <v>62</v>
@@ -3449,39 +3463,39 @@
         <v>44</v>
       </c>
       <c r="H40" t="s">
-        <v>128</v>
+        <v>70</v>
       </c>
       <c r="I40" t="s">
         <v>44</v>
       </c>
       <c r="J40" t="s">
-        <v>51</v>
+        <v>184</v>
       </c>
       <c r="K40" t="s">
-        <v>205</v>
+        <v>185</v>
       </c>
       <c r="L40" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="M40" t="s">
-        <v>51</v>
+        <v>186</v>
       </c>
       <c r="N40" t="s">
-        <v>74</v>
+        <v>52</v>
       </c>
     </row>
     <row r="41" spans="1:14">
       <c r="A41" t="s">
-        <v>206</v>
+        <v>187</v>
       </c>
       <c r="B41" t="s">
-        <v>207</v>
-      </c>
-      <c r="C41" t="s">
-        <v>44</v>
+        <v>80</v>
+      </c>
+      <c r="C41">
+        <v>3</v>
       </c>
       <c r="D41" t="s">
-        <v>117</v>
+        <v>62</v>
       </c>
       <c r="E41" t="s">
         <v>81</v>
@@ -3493,22 +3507,22 @@
         <v>44</v>
       </c>
       <c r="H41" t="s">
-        <v>133</v>
+        <v>70</v>
       </c>
       <c r="I41" t="s">
         <v>44</v>
       </c>
       <c r="J41" t="s">
-        <v>51</v>
+        <v>188</v>
       </c>
       <c r="K41" t="s">
-        <v>208</v>
+        <v>189</v>
       </c>
       <c r="L41" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="M41" t="s">
-        <v>51</v>
+        <v>190</v>
       </c>
       <c r="N41" t="s">
         <v>59</v>
@@ -3516,16 +3530,16 @@
     </row>
     <row r="42" spans="1:14">
       <c r="A42" t="s">
-        <v>209</v>
+        <v>191</v>
       </c>
       <c r="B42" t="s">
-        <v>147</v>
-      </c>
-      <c r="C42" t="s">
-        <v>165</v>
+        <v>80</v>
+      </c>
+      <c r="C42">
+        <v>3</v>
       </c>
       <c r="D42" t="s">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="E42" t="s">
         <v>81</v>
@@ -3537,22 +3551,22 @@
         <v>44</v>
       </c>
       <c r="H42" t="s">
-        <v>138</v>
+        <v>70</v>
       </c>
       <c r="I42" t="s">
         <v>44</v>
       </c>
       <c r="J42" t="s">
-        <v>51</v>
+        <v>192</v>
       </c>
       <c r="K42" t="s">
-        <v>210</v>
+        <v>193</v>
       </c>
       <c r="L42" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="M42" t="s">
-        <v>51</v>
+        <v>94</v>
       </c>
       <c r="N42" t="s">
         <v>59</v>
@@ -3560,16 +3574,16 @@
     </row>
     <row r="43" spans="1:14">
       <c r="A43" t="s">
-        <v>211</v>
+        <v>194</v>
       </c>
       <c r="B43" t="s">
-        <v>150</v>
-      </c>
-      <c r="C43" t="s">
-        <v>165</v>
+        <v>80</v>
+      </c>
+      <c r="C43">
+        <v>3</v>
       </c>
       <c r="D43" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="E43" t="s">
         <v>81</v>
@@ -3581,36 +3595,36 @@
         <v>44</v>
       </c>
       <c r="H43" t="s">
-        <v>143</v>
+        <v>70</v>
       </c>
       <c r="I43" t="s">
         <v>44</v>
       </c>
       <c r="J43" t="s">
-        <v>51</v>
+        <v>195</v>
       </c>
       <c r="K43" t="s">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="L43" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="M43" t="s">
-        <v>51</v>
+        <v>197</v>
       </c>
       <c r="N43" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
     </row>
     <row r="44" spans="1:14">
       <c r="A44" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="B44" t="s">
         <v>80</v>
       </c>
-      <c r="C44" t="s">
-        <v>165</v>
+      <c r="C44">
+        <v>3</v>
       </c>
       <c r="D44" t="s">
         <v>62</v>
@@ -3625,39 +3639,39 @@
         <v>44</v>
       </c>
       <c r="H44" t="s">
-        <v>128</v>
+        <v>107</v>
       </c>
       <c r="I44" t="s">
         <v>44</v>
       </c>
       <c r="J44" t="s">
-        <v>51</v>
+        <v>199</v>
       </c>
       <c r="K44" t="s">
-        <v>214</v>
+        <v>200</v>
       </c>
       <c r="L44" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="M44" t="s">
-        <v>51</v>
+        <v>201</v>
       </c>
       <c r="N44" t="s">
-        <v>74</v>
+        <v>52</v>
       </c>
     </row>
     <row r="45" spans="1:14">
       <c r="A45" t="s">
-        <v>215</v>
+        <v>202</v>
       </c>
       <c r="B45" t="s">
-        <v>207</v>
-      </c>
-      <c r="C45" t="s">
-        <v>165</v>
+        <v>80</v>
+      </c>
+      <c r="C45">
+        <v>3</v>
       </c>
       <c r="D45" t="s">
-        <v>117</v>
+        <v>62</v>
       </c>
       <c r="E45" t="s">
         <v>81</v>
@@ -3669,22 +3683,22 @@
         <v>44</v>
       </c>
       <c r="H45" t="s">
-        <v>143</v>
+        <v>111</v>
       </c>
       <c r="I45" t="s">
         <v>44</v>
       </c>
       <c r="J45" t="s">
-        <v>51</v>
+        <v>203</v>
       </c>
       <c r="K45" t="s">
-        <v>216</v>
+        <v>204</v>
       </c>
       <c r="L45" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="M45" t="s">
-        <v>51</v>
+        <v>205</v>
       </c>
       <c r="N45" t="s">
         <v>52</v>
@@ -3692,16 +3706,16 @@
     </row>
     <row r="46" spans="1:14">
       <c r="A46" t="s">
-        <v>217</v>
+        <v>206</v>
       </c>
       <c r="B46" t="s">
-        <v>218</v>
-      </c>
-      <c r="C46" t="s">
-        <v>197</v>
+        <v>96</v>
+      </c>
+      <c r="C46">
+        <v>4</v>
       </c>
       <c r="D46" t="s">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="E46" t="s">
         <v>97</v>
@@ -3713,42 +3727,42 @@
         <v>44</v>
       </c>
       <c r="H46" t="s">
-        <v>143</v>
+        <v>118</v>
       </c>
       <c r="I46" t="s">
         <v>44</v>
       </c>
       <c r="J46" t="s">
-        <v>51</v>
+        <v>207</v>
       </c>
       <c r="K46" t="s">
-        <v>219</v>
+        <v>208</v>
       </c>
       <c r="L46" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="M46" t="s">
-        <v>51</v>
+        <v>106</v>
       </c>
       <c r="N46" t="s">
-        <v>74</v>
+        <v>59</v>
       </c>
     </row>
     <row r="47" spans="1:14">
       <c r="A47" t="s">
-        <v>141</v>
+        <v>209</v>
       </c>
       <c r="B47" t="s">
-        <v>142</v>
-      </c>
-      <c r="C47" t="s">
-        <v>197</v>
+        <v>92</v>
+      </c>
+      <c r="C47">
+        <v>4</v>
       </c>
       <c r="D47" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="E47" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="F47" t="s">
         <v>44</v>
@@ -3757,42 +3771,42 @@
         <v>44</v>
       </c>
       <c r="H47" t="s">
-        <v>143</v>
+        <v>123</v>
       </c>
       <c r="I47" t="s">
         <v>44</v>
       </c>
       <c r="J47" t="s">
-        <v>51</v>
+        <v>210</v>
       </c>
       <c r="K47" t="s">
-        <v>145</v>
+        <v>211</v>
       </c>
       <c r="L47" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="M47" t="s">
-        <v>51</v>
+        <v>212</v>
       </c>
       <c r="N47" t="s">
-        <v>74</v>
+        <v>52</v>
       </c>
     </row>
     <row r="48" spans="1:14">
       <c r="A48" t="s">
-        <v>95</v>
+        <v>213</v>
       </c>
       <c r="B48" t="s">
-        <v>96</v>
-      </c>
-      <c r="C48" t="s">
-        <v>197</v>
+        <v>80</v>
+      </c>
+      <c r="C48">
+        <v>2</v>
       </c>
       <c r="D48" t="s">
         <v>62</v>
       </c>
       <c r="E48" t="s">
-        <v>97</v>
+        <v>81</v>
       </c>
       <c r="F48" t="s">
         <v>44</v>
@@ -3801,7 +3815,7 @@
         <v>44</v>
       </c>
       <c r="H48" t="s">
-        <v>143</v>
+        <v>128</v>
       </c>
       <c r="I48" t="s">
         <v>44</v>
@@ -3810,7 +3824,7 @@
         <v>51</v>
       </c>
       <c r="K48" t="s">
-        <v>220</v>
+        <v>165</v>
       </c>
       <c r="L48" t="s">
         <v>50</v>
@@ -3819,24 +3833,24 @@
         <v>51</v>
       </c>
       <c r="N48" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
     </row>
     <row r="49" spans="1:14">
       <c r="A49" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="B49" t="s">
-        <v>222</v>
-      </c>
-      <c r="C49" t="s">
-        <v>197</v>
+        <v>167</v>
+      </c>
+      <c r="C49">
+        <v>2</v>
       </c>
       <c r="D49" t="s">
         <v>117</v>
       </c>
       <c r="E49" t="s">
-        <v>97</v>
+        <v>81</v>
       </c>
       <c r="F49" t="s">
         <v>44</v>
@@ -3845,7 +3859,7 @@
         <v>44</v>
       </c>
       <c r="H49" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="I49" t="s">
         <v>44</v>
@@ -3854,7 +3868,7 @@
         <v>51</v>
       </c>
       <c r="K49" t="s">
-        <v>223</v>
+        <v>168</v>
       </c>
       <c r="L49" t="s">
         <v>50</v>
@@ -3868,19 +3882,19 @@
     </row>
     <row r="50" spans="1:14">
       <c r="A50" t="s">
-        <v>136</v>
+        <v>215</v>
       </c>
       <c r="B50" t="s">
-        <v>137</v>
-      </c>
-      <c r="C50" t="s">
-        <v>197</v>
+        <v>147</v>
+      </c>
+      <c r="C50">
+        <v>3</v>
       </c>
       <c r="D50" t="s">
         <v>45</v>
       </c>
       <c r="E50" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="F50" t="s">
         <v>44</v>
@@ -3889,7 +3903,7 @@
         <v>44</v>
       </c>
       <c r="H50" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="I50" t="s">
         <v>44</v>
@@ -3898,7 +3912,7 @@
         <v>51</v>
       </c>
       <c r="K50" t="s">
-        <v>140</v>
+        <v>216</v>
       </c>
       <c r="L50" t="s">
         <v>50</v>
@@ -3912,19 +3926,19 @@
     </row>
     <row r="51" spans="1:14">
       <c r="A51" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="B51" t="s">
-        <v>225</v>
-      </c>
-      <c r="C51" t="s">
-        <v>197</v>
+        <v>150</v>
+      </c>
+      <c r="C51">
+        <v>3</v>
       </c>
       <c r="D51" t="s">
         <v>55</v>
       </c>
       <c r="E51" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="F51" t="s">
         <v>44</v>
@@ -3942,7 +3956,7 @@
         <v>51</v>
       </c>
       <c r="K51" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="L51" t="s">
         <v>50</v>
@@ -3951,24 +3965,24 @@
         <v>51</v>
       </c>
       <c r="N51" t="s">
-        <v>74</v>
+        <v>59</v>
       </c>
     </row>
     <row r="52" spans="1:14">
       <c r="A52" t="s">
-        <v>91</v>
+        <v>219</v>
       </c>
       <c r="B52" t="s">
-        <v>92</v>
-      </c>
-      <c r="C52" t="s">
-        <v>197</v>
+        <v>80</v>
+      </c>
+      <c r="C52">
+        <v>3</v>
       </c>
       <c r="D52" t="s">
         <v>62</v>
       </c>
       <c r="E52" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="F52" t="s">
         <v>44</v>
@@ -3977,7 +3991,7 @@
         <v>44</v>
       </c>
       <c r="H52" t="s">
-        <v>143</v>
+        <v>128</v>
       </c>
       <c r="I52" t="s">
         <v>44</v>
@@ -3986,7 +4000,7 @@
         <v>51</v>
       </c>
       <c r="K52" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="L52" t="s">
         <v>50</v>
@@ -3995,24 +4009,24 @@
         <v>51</v>
       </c>
       <c r="N52" t="s">
-        <v>52</v>
+        <v>74</v>
       </c>
     </row>
     <row r="53" spans="1:14">
       <c r="A53" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="B53" t="s">
-        <v>229</v>
-      </c>
-      <c r="C53" t="s">
-        <v>197</v>
+        <v>167</v>
+      </c>
+      <c r="C53">
+        <v>3</v>
       </c>
       <c r="D53" t="s">
         <v>117</v>
       </c>
       <c r="E53" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="F53" t="s">
         <v>44</v>
@@ -4030,7 +4044,7 @@
         <v>51</v>
       </c>
       <c r="K53" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="L53" t="s">
         <v>50</v>
@@ -4039,6 +4053,358 @@
         <v>51</v>
       </c>
       <c r="N53" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14">
+      <c r="A54" t="s">
+        <v>223</v>
+      </c>
+      <c r="B54" t="s">
+        <v>224</v>
+      </c>
+      <c r="C54">
+        <v>4</v>
+      </c>
+      <c r="D54" t="s">
+        <v>45</v>
+      </c>
+      <c r="E54" t="s">
+        <v>97</v>
+      </c>
+      <c r="F54" t="s">
+        <v>44</v>
+      </c>
+      <c r="G54" t="s">
+        <v>44</v>
+      </c>
+      <c r="H54" t="s">
+        <v>143</v>
+      </c>
+      <c r="I54" t="s">
+        <v>44</v>
+      </c>
+      <c r="J54" t="s">
+        <v>51</v>
+      </c>
+      <c r="K54" t="s">
+        <v>225</v>
+      </c>
+      <c r="L54" t="s">
+        <v>50</v>
+      </c>
+      <c r="M54" t="s">
+        <v>51</v>
+      </c>
+      <c r="N54" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14">
+      <c r="A55" t="s">
+        <v>141</v>
+      </c>
+      <c r="B55" t="s">
+        <v>142</v>
+      </c>
+      <c r="C55">
+        <v>4</v>
+      </c>
+      <c r="D55" t="s">
+        <v>55</v>
+      </c>
+      <c r="E55" t="s">
+        <v>97</v>
+      </c>
+      <c r="F55" t="s">
+        <v>44</v>
+      </c>
+      <c r="G55" t="s">
+        <v>44</v>
+      </c>
+      <c r="H55" t="s">
+        <v>143</v>
+      </c>
+      <c r="I55" t="s">
+        <v>44</v>
+      </c>
+      <c r="J55" t="s">
+        <v>51</v>
+      </c>
+      <c r="K55" t="s">
+        <v>145</v>
+      </c>
+      <c r="L55" t="s">
+        <v>50</v>
+      </c>
+      <c r="M55" t="s">
+        <v>51</v>
+      </c>
+      <c r="N55" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14">
+      <c r="A56" t="s">
+        <v>95</v>
+      </c>
+      <c r="B56" t="s">
+        <v>96</v>
+      </c>
+      <c r="C56">
+        <v>4</v>
+      </c>
+      <c r="D56" t="s">
+        <v>62</v>
+      </c>
+      <c r="E56" t="s">
+        <v>97</v>
+      </c>
+      <c r="F56" t="s">
+        <v>44</v>
+      </c>
+      <c r="G56" t="s">
+        <v>44</v>
+      </c>
+      <c r="H56" t="s">
+        <v>143</v>
+      </c>
+      <c r="I56" t="s">
+        <v>44</v>
+      </c>
+      <c r="J56" t="s">
+        <v>51</v>
+      </c>
+      <c r="K56" t="s">
+        <v>226</v>
+      </c>
+      <c r="L56" t="s">
+        <v>50</v>
+      </c>
+      <c r="M56" t="s">
+        <v>51</v>
+      </c>
+      <c r="N56" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="57" spans="1:14">
+      <c r="A57" t="s">
+        <v>227</v>
+      </c>
+      <c r="B57" t="s">
+        <v>228</v>
+      </c>
+      <c r="C57">
+        <v>4</v>
+      </c>
+      <c r="D57" t="s">
+        <v>117</v>
+      </c>
+      <c r="E57" t="s">
+        <v>97</v>
+      </c>
+      <c r="F57" t="s">
+        <v>44</v>
+      </c>
+      <c r="G57" t="s">
+        <v>44</v>
+      </c>
+      <c r="H57" t="s">
+        <v>143</v>
+      </c>
+      <c r="I57" t="s">
+        <v>44</v>
+      </c>
+      <c r="J57" t="s">
+        <v>51</v>
+      </c>
+      <c r="K57" t="s">
+        <v>229</v>
+      </c>
+      <c r="L57" t="s">
+        <v>50</v>
+      </c>
+      <c r="M57" t="s">
+        <v>51</v>
+      </c>
+      <c r="N57" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="58" spans="1:14">
+      <c r="A58" t="s">
+        <v>136</v>
+      </c>
+      <c r="B58" t="s">
+        <v>137</v>
+      </c>
+      <c r="C58">
+        <v>4</v>
+      </c>
+      <c r="D58" t="s">
+        <v>45</v>
+      </c>
+      <c r="E58" t="s">
+        <v>93</v>
+      </c>
+      <c r="F58" t="s">
+        <v>44</v>
+      </c>
+      <c r="G58" t="s">
+        <v>44</v>
+      </c>
+      <c r="H58" t="s">
+        <v>143</v>
+      </c>
+      <c r="I58" t="s">
+        <v>44</v>
+      </c>
+      <c r="J58" t="s">
+        <v>51</v>
+      </c>
+      <c r="K58" t="s">
+        <v>140</v>
+      </c>
+      <c r="L58" t="s">
+        <v>50</v>
+      </c>
+      <c r="M58" t="s">
+        <v>51</v>
+      </c>
+      <c r="N58" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="59" spans="1:14">
+      <c r="A59" t="s">
+        <v>230</v>
+      </c>
+      <c r="B59" t="s">
+        <v>231</v>
+      </c>
+      <c r="C59">
+        <v>4</v>
+      </c>
+      <c r="D59" t="s">
+        <v>55</v>
+      </c>
+      <c r="E59" t="s">
+        <v>93</v>
+      </c>
+      <c r="F59" t="s">
+        <v>44</v>
+      </c>
+      <c r="G59" t="s">
+        <v>44</v>
+      </c>
+      <c r="H59" t="s">
+        <v>143</v>
+      </c>
+      <c r="I59" t="s">
+        <v>44</v>
+      </c>
+      <c r="J59" t="s">
+        <v>51</v>
+      </c>
+      <c r="K59" t="s">
+        <v>232</v>
+      </c>
+      <c r="L59" t="s">
+        <v>50</v>
+      </c>
+      <c r="M59" t="s">
+        <v>51</v>
+      </c>
+      <c r="N59" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="60" spans="1:14">
+      <c r="A60" t="s">
+        <v>91</v>
+      </c>
+      <c r="B60" t="s">
+        <v>92</v>
+      </c>
+      <c r="C60">
+        <v>4</v>
+      </c>
+      <c r="D60" t="s">
+        <v>62</v>
+      </c>
+      <c r="E60" t="s">
+        <v>93</v>
+      </c>
+      <c r="F60" t="s">
+        <v>44</v>
+      </c>
+      <c r="G60" t="s">
+        <v>44</v>
+      </c>
+      <c r="H60" t="s">
+        <v>143</v>
+      </c>
+      <c r="I60" t="s">
+        <v>44</v>
+      </c>
+      <c r="J60" t="s">
+        <v>51</v>
+      </c>
+      <c r="K60" t="s">
+        <v>233</v>
+      </c>
+      <c r="L60" t="s">
+        <v>50</v>
+      </c>
+      <c r="M60" t="s">
+        <v>51</v>
+      </c>
+      <c r="N60" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="61" spans="1:14">
+      <c r="A61" t="s">
+        <v>234</v>
+      </c>
+      <c r="B61" t="s">
+        <v>235</v>
+      </c>
+      <c r="C61">
+        <v>4</v>
+      </c>
+      <c r="D61" t="s">
+        <v>117</v>
+      </c>
+      <c r="E61" t="s">
+        <v>93</v>
+      </c>
+      <c r="F61" t="s">
+        <v>44</v>
+      </c>
+      <c r="G61" t="s">
+        <v>44</v>
+      </c>
+      <c r="H61" t="s">
+        <v>143</v>
+      </c>
+      <c r="I61" t="s">
+        <v>44</v>
+      </c>
+      <c r="J61" t="s">
+        <v>51</v>
+      </c>
+      <c r="K61" t="s">
+        <v>236</v>
+      </c>
+      <c r="L61" t="s">
+        <v>50</v>
+      </c>
+      <c r="M61" t="s">
+        <v>51</v>
+      </c>
+      <c r="N61" t="s">
         <v>74</v>
       </c>
     </row>

--- a/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/制造_躯体材料配置表_Manufacture_BodyPartConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/制造_躯体材料配置表_Manufacture_BodyPartConfig.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="816" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="816" uniqueCount="241">
   <si>
     <t>躯体ID</t>
   </si>
@@ -499,6 +499,9 @@
     <t>Art_BP_Arm_Undead_Warrior</t>
   </si>
   <si>
+    <t>Class_Warrior_0</t>
+  </si>
+  <si>
     <t>BP_Arm_Undead_Archer_0</t>
   </si>
   <si>
@@ -508,6 +511,9 @@
     <t>Art_BP_Arm_Undead_Archer</t>
   </si>
   <si>
+    <t>Class_Archer_0</t>
+  </si>
+  <si>
     <t>BP_Arm_Undead_Mage_0</t>
   </si>
   <si>
@@ -517,6 +523,9 @@
     <t>Art_BP_Arm_Undead_Mage</t>
   </si>
   <si>
+    <t>Class_Mage_0</t>
+  </si>
+  <si>
     <t>BP_Arm_Undead_Rogue_0</t>
   </si>
   <si>
@@ -524,6 +533,9 @@
   </si>
   <si>
     <t>Art_BP_Arm_Undead_Rogue</t>
+  </si>
+  <si>
+    <t>Class_Rogue_0</t>
   </si>
   <si>
     <t>BP_Arm_Undead_0</t>
@@ -1223,148 +1235,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="34" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1722,6 +1734,7 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="24.625" customWidth="1"/>
+    <col min="13" max="13" width="26.875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14">
@@ -2862,7 +2875,7 @@
         <v>44</v>
       </c>
       <c r="M26" t="s">
-        <v>66</v>
+        <v>155</v>
       </c>
       <c r="N26" t="s">
         <v>59</v>
@@ -2870,7 +2883,7 @@
     </row>
     <row r="27" spans="1:14">
       <c r="A27" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B27" t="s">
         <v>80</v>
@@ -2897,16 +2910,16 @@
         <v>44</v>
       </c>
       <c r="J27" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="K27" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="L27" t="s">
         <v>44</v>
       </c>
       <c r="M27" t="s">
-        <v>73</v>
+        <v>159</v>
       </c>
       <c r="N27" t="s">
         <v>74</v>
@@ -2914,7 +2927,7 @@
     </row>
     <row r="28" spans="1:14">
       <c r="A28" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B28" t="s">
         <v>80</v>
@@ -2941,16 +2954,16 @@
         <v>44</v>
       </c>
       <c r="J28" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="K28" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="L28" t="s">
         <v>44</v>
       </c>
       <c r="M28" t="s">
-        <v>78</v>
+        <v>163</v>
       </c>
       <c r="N28" t="s">
         <v>52</v>
@@ -2958,7 +2971,7 @@
     </row>
     <row r="29" spans="1:14">
       <c r="A29" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B29" t="s">
         <v>80</v>
@@ -2985,16 +2998,16 @@
         <v>44</v>
       </c>
       <c r="J29" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="K29" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="L29" t="s">
         <v>44</v>
       </c>
       <c r="M29" t="s">
-        <v>86</v>
+        <v>167</v>
       </c>
       <c r="N29" t="s">
         <v>74</v>
@@ -3002,7 +3015,7 @@
     </row>
     <row r="30" spans="1:14">
       <c r="A30" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="B30" t="s">
         <v>80</v>
@@ -3032,7 +3045,7 @@
         <v>51</v>
       </c>
       <c r="K30" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="L30" t="s">
         <v>50</v>
@@ -3046,10 +3059,10 @@
     </row>
     <row r="31" spans="1:14">
       <c r="A31" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="B31" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="C31">
         <v>1</v>
@@ -3076,7 +3089,7 @@
         <v>51</v>
       </c>
       <c r="K31" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="L31" t="s">
         <v>50</v>
@@ -3090,7 +3103,7 @@
     </row>
     <row r="32" spans="1:14">
       <c r="A32" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="B32" t="s">
         <v>147</v>
@@ -3134,7 +3147,7 @@
     </row>
     <row r="33" spans="1:14">
       <c r="A33" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="B33" t="s">
         <v>150</v>
@@ -3178,7 +3191,7 @@
     </row>
     <row r="34" spans="1:14">
       <c r="A34" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="B34" t="s">
         <v>80</v>
@@ -3222,7 +3235,7 @@
     </row>
     <row r="35" spans="1:14">
       <c r="A35" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="B35" t="s">
         <v>80</v>
@@ -3249,10 +3262,10 @@
         <v>44</v>
       </c>
       <c r="J35" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="K35" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="L35" t="s">
         <v>44</v>
@@ -3266,7 +3279,7 @@
     </row>
     <row r="36" spans="1:14">
       <c r="A36" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="B36" t="s">
         <v>80</v>
@@ -3293,10 +3306,10 @@
         <v>44</v>
       </c>
       <c r="J36" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="K36" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="L36" t="s">
         <v>44</v>
@@ -3310,7 +3323,7 @@
     </row>
     <row r="37" spans="1:14">
       <c r="A37" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="B37" t="s">
         <v>80</v>
@@ -3337,10 +3350,10 @@
         <v>44</v>
       </c>
       <c r="J37" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="K37" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="L37" t="s">
         <v>44</v>
@@ -3354,7 +3367,7 @@
     </row>
     <row r="38" spans="1:14">
       <c r="A38" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="B38" t="s">
         <v>80</v>
@@ -3381,16 +3394,16 @@
         <v>44</v>
       </c>
       <c r="J38" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="K38" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="L38" t="s">
         <v>44</v>
       </c>
       <c r="M38" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="N38" t="s">
         <v>59</v>
@@ -3398,7 +3411,7 @@
     </row>
     <row r="39" spans="1:14">
       <c r="A39" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="B39" t="s">
         <v>80</v>
@@ -3425,16 +3438,16 @@
         <v>44</v>
       </c>
       <c r="J39" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="K39" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="L39" t="s">
         <v>44</v>
       </c>
       <c r="M39" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="N39" t="s">
         <v>74</v>
@@ -3442,7 +3455,7 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="B40" t="s">
         <v>80</v>
@@ -3469,16 +3482,16 @@
         <v>44</v>
       </c>
       <c r="J40" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="K40" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="L40" t="s">
         <v>44</v>
       </c>
       <c r="M40" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="N40" t="s">
         <v>52</v>
@@ -3486,7 +3499,7 @@
     </row>
     <row r="41" spans="1:14">
       <c r="A41" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="B41" t="s">
         <v>80</v>
@@ -3513,16 +3526,16 @@
         <v>44</v>
       </c>
       <c r="J41" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="K41" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="L41" t="s">
         <v>44</v>
       </c>
       <c r="M41" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="N41" t="s">
         <v>59</v>
@@ -3530,7 +3543,7 @@
     </row>
     <row r="42" spans="1:14">
       <c r="A42" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="B42" t="s">
         <v>80</v>
@@ -3557,10 +3570,10 @@
         <v>44</v>
       </c>
       <c r="J42" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="K42" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="L42" t="s">
         <v>44</v>
@@ -3574,7 +3587,7 @@
     </row>
     <row r="43" spans="1:14">
       <c r="A43" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="B43" t="s">
         <v>80</v>
@@ -3601,16 +3614,16 @@
         <v>44</v>
       </c>
       <c r="J43" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="K43" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="L43" t="s">
         <v>44</v>
       </c>
       <c r="M43" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="N43" t="s">
         <v>74</v>
@@ -3618,7 +3631,7 @@
     </row>
     <row r="44" spans="1:14">
       <c r="A44" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="B44" t="s">
         <v>80</v>
@@ -3645,16 +3658,16 @@
         <v>44</v>
       </c>
       <c r="J44" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="K44" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="L44" t="s">
         <v>44</v>
       </c>
       <c r="M44" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="N44" t="s">
         <v>52</v>
@@ -3662,7 +3675,7 @@
     </row>
     <row r="45" spans="1:14">
       <c r="A45" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="B45" t="s">
         <v>80</v>
@@ -3689,16 +3702,16 @@
         <v>44</v>
       </c>
       <c r="J45" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="K45" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="L45" t="s">
         <v>44</v>
       </c>
       <c r="M45" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="N45" t="s">
         <v>52</v>
@@ -3706,7 +3719,7 @@
     </row>
     <row r="46" spans="1:14">
       <c r="A46" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="B46" t="s">
         <v>96</v>
@@ -3733,10 +3746,10 @@
         <v>44</v>
       </c>
       <c r="J46" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="K46" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="L46" t="s">
         <v>44</v>
@@ -3750,7 +3763,7 @@
     </row>
     <row r="47" spans="1:14">
       <c r="A47" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="B47" t="s">
         <v>92</v>
@@ -3777,16 +3790,16 @@
         <v>44</v>
       </c>
       <c r="J47" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="K47" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="L47" t="s">
         <v>44</v>
       </c>
       <c r="M47" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="N47" t="s">
         <v>52</v>
@@ -3794,7 +3807,7 @@
     </row>
     <row r="48" spans="1:14">
       <c r="A48" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="B48" t="s">
         <v>80</v>
@@ -3824,7 +3837,7 @@
         <v>51</v>
       </c>
       <c r="K48" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="L48" t="s">
         <v>50</v>
@@ -3838,10 +3851,10 @@
     </row>
     <row r="49" spans="1:14">
       <c r="A49" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="B49" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="C49">
         <v>2</v>
@@ -3868,7 +3881,7 @@
         <v>51</v>
       </c>
       <c r="K49" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="L49" t="s">
         <v>50</v>
@@ -3882,7 +3895,7 @@
     </row>
     <row r="50" spans="1:14">
       <c r="A50" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="B50" t="s">
         <v>147</v>
@@ -3912,7 +3925,7 @@
         <v>51</v>
       </c>
       <c r="K50" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="L50" t="s">
         <v>50</v>
@@ -3926,7 +3939,7 @@
     </row>
     <row r="51" spans="1:14">
       <c r="A51" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="B51" t="s">
         <v>150</v>
@@ -3956,7 +3969,7 @@
         <v>51</v>
       </c>
       <c r="K51" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="L51" t="s">
         <v>50</v>
@@ -3970,7 +3983,7 @@
     </row>
     <row r="52" spans="1:14">
       <c r="A52" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="B52" t="s">
         <v>80</v>
@@ -4000,7 +4013,7 @@
         <v>51</v>
       </c>
       <c r="K52" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="L52" t="s">
         <v>50</v>
@@ -4014,10 +4027,10 @@
     </row>
     <row r="53" spans="1:14">
       <c r="A53" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="B53" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="C53">
         <v>3</v>
@@ -4044,7 +4057,7 @@
         <v>51</v>
       </c>
       <c r="K53" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="L53" t="s">
         <v>50</v>
@@ -4058,10 +4071,10 @@
     </row>
     <row r="54" spans="1:14">
       <c r="A54" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="B54" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="C54">
         <v>4</v>
@@ -4088,7 +4101,7 @@
         <v>51</v>
       </c>
       <c r="K54" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="L54" t="s">
         <v>50</v>
@@ -4176,7 +4189,7 @@
         <v>51</v>
       </c>
       <c r="K56" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="L56" t="s">
         <v>50</v>
@@ -4190,10 +4203,10 @@
     </row>
     <row r="57" spans="1:14">
       <c r="A57" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="B57" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="C57">
         <v>4</v>
@@ -4220,7 +4233,7 @@
         <v>51</v>
       </c>
       <c r="K57" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="L57" t="s">
         <v>50</v>
@@ -4278,10 +4291,10 @@
     </row>
     <row r="59" spans="1:14">
       <c r="A59" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="B59" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="C59">
         <v>4</v>
@@ -4308,7 +4321,7 @@
         <v>51</v>
       </c>
       <c r="K59" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="L59" t="s">
         <v>50</v>
@@ -4352,7 +4365,7 @@
         <v>51</v>
       </c>
       <c r="K60" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="L60" t="s">
         <v>50</v>
@@ -4366,10 +4379,10 @@
     </row>
     <row r="61" spans="1:14">
       <c r="A61" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="B61" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="C61">
         <v>4</v>
@@ -4396,7 +4409,7 @@
         <v>51</v>
       </c>
       <c r="K61" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="L61" t="s">
         <v>50</v>

--- a/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/制造_躯体材料配置表_Manufacture_BodyPartConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/制造_躯体材料配置表_Manufacture_BodyPartConfig.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Work\Cursor\Gravedigger2026\Gravedigger2026\Gravedigger2026\Assets\ConfigTables\Mode2\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\CursorGame_Git\Gravedigger2026\Gravedigger2026\Assets\ConfigTables\Mode2\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="25600" windowHeight="12080"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1731,10 +1731,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:N61"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="24.625" customWidth="1"/>
-    <col min="13" max="13" width="26.875" customWidth="1"/>
+    <col min="1" max="1" width="24.6272727272727" customWidth="1"/>
+    <col min="8" max="8" width="68.7272727272727" customWidth="1"/>
+    <col min="13" max="13" width="26.8727272727273" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14">

--- a/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/制造_躯体材料配置表_Manufacture_BodyPartConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/制造_躯体材料配置表_Manufacture_BodyPartConfig.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="536" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="536" uniqueCount="171">
   <si>
     <t>躯体ID</t>
   </si>
@@ -175,7 +175,7 @@
     <t>1</t>
   </si>
   <si>
-    <t>MaxHP_20|Strength_8|Agility_16|Intelligence_24|MoveSpeed_0.1</t>
+    <t>MaxHP_10|Strength_5|Agility_5|Intelligence_5</t>
   </si>
   <si>
     <t/>
@@ -199,9 +199,6 @@
     <t>Torso</t>
   </si>
   <si>
-    <t>MaxHP_25|Strength_16|Agility_24|Intelligence_4|MoveSpeed_0.2</t>
-  </si>
-  <si>
     <t>Art_BP_Torso_Undead_1</t>
   </si>
   <si>
@@ -217,9 +214,6 @@
     <t>Arm</t>
   </si>
   <si>
-    <t>MaxHP_30|Strength_24|Agility_4|Intelligence_8|MoveSpeed_0.3</t>
-  </si>
-  <si>
     <t>战士</t>
   </si>
   <si>
@@ -232,9 +226,6 @@
     <t>BP_Arm_Undead_Archer_0</t>
   </si>
   <si>
-    <t>MaxHP_50|Strength_24|Agility_4|Intelligence_8|MoveSpeed_0.1</t>
-  </si>
-  <si>
     <t>射手</t>
   </si>
   <si>
@@ -274,9 +265,6 @@
     <t>BP_Arm_Undead_0</t>
   </si>
   <si>
-    <t>MaxHP_45|Strength_16|Agility_24|Intelligence_4|MoveSpeed_0.3</t>
-  </si>
-  <si>
     <t>Art_BP_Arm_Undead_1</t>
   </si>
   <si>
@@ -289,15 +277,15 @@
     <t>Leg</t>
   </si>
   <si>
-    <t>MaxHP_55|Strength_4|Agility_8|Intelligence_16|MoveSpeed_0.2</t>
-  </si>
-  <si>
     <t>Art_BP_Leg_Undead_1</t>
   </si>
   <si>
     <t>BP_Head_Undead_1</t>
   </si>
   <si>
+    <t>MaxHP_20|Strength_10|Agility_10|Intelligence_10</t>
+  </si>
+  <si>
     <t>BP_Torso_Undead_1</t>
   </si>
   <si>
@@ -328,6 +316,9 @@
     <t>BP_Arm_Undead_Guardian</t>
   </si>
   <si>
+    <t>MaxHP_30|Strength_15|Agility_15|Intelligence_15</t>
+  </si>
+  <si>
     <t>近卫</t>
   </si>
   <si>
@@ -400,9 +391,6 @@
     <t>BP_Arm_Undead_FireMage</t>
   </si>
   <si>
-    <t>MaxHP_28|Strength_12|Agility_12|Intelligence_8|MoveSpeed_0.2</t>
-  </si>
-  <si>
     <t>火法</t>
   </si>
   <si>
@@ -415,9 +403,6 @@
     <t>BP_Arm_Undead_Shadowblade</t>
   </si>
   <si>
-    <t>MaxHP_48|Strength_20|Agility_8|Intelligence_8|MoveSpeed_0.2</t>
-  </si>
-  <si>
     <t>影刃</t>
   </si>
   <si>
@@ -436,7 +421,7 @@
     <t>Race_Angel</t>
   </si>
   <si>
-    <t>MaxHP_35|Strength_4|Agility_8|Intelligence_16|MoveSpeed_0.1</t>
+    <t>MaxHP_40|Strength_20|Agility_20|Intelligence_20</t>
   </si>
   <si>
     <t>圣骑士</t>
@@ -457,9 +442,6 @@
     <t>Race_Demon</t>
   </si>
   <si>
-    <t>MaxHP_40|Strength_8|Agility_16|Intelligence_24|MoveSpeed_0.2</t>
-  </si>
-  <si>
     <t>暗黑法师</t>
   </si>
   <si>
@@ -478,16 +460,10 @@
     <t>BP_Head_Undead_2</t>
   </si>
   <si>
-    <t>MaxHP_60|Strength_8|Agility_16|Intelligence_24|MoveSpeed_0.3</t>
-  </si>
-  <si>
     <t>Art_BP_Head_Undead_2</t>
   </si>
   <si>
     <t>BP_Torso_Undead_2</t>
-  </si>
-  <si>
-    <t>MaxHP_65|Strength_16|Agility_24|Intelligence_4|MoveSpeed_0.1</t>
   </si>
   <si>
     <t>Art_BP_Torso_Undead_2</t>
@@ -1541,7 +1517,8 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="24.625" customWidth="1"/>
-    <col min="8" max="8" width="68.725" customWidth="1"/>
+    <col min="5" max="5" width="12.875" customWidth="1"/>
+    <col min="8" max="8" width="48.75" customWidth="1"/>
     <col min="13" max="13" width="26.875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1744,16 +1721,16 @@
         <v>46</v>
       </c>
       <c r="H5" t="s">
+        <v>47</v>
+      </c>
+      <c r="I5" t="s">
+        <v>46</v>
+      </c>
+      <c r="J5" t="s">
+        <v>48</v>
+      </c>
+      <c r="K5" t="s">
         <v>55</v>
-      </c>
-      <c r="I5" t="s">
-        <v>46</v>
-      </c>
-      <c r="J5" t="s">
-        <v>48</v>
-      </c>
-      <c r="K5" t="s">
-        <v>56</v>
       </c>
       <c r="L5" t="s">
         <v>50</v>
@@ -1762,21 +1739,21 @@
         <v>48</v>
       </c>
       <c r="N5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6" spans="1:14">
       <c r="A6" t="s">
+        <v>57</v>
+      </c>
+      <c r="B6" t="s">
         <v>58</v>
-      </c>
-      <c r="B6" t="s">
-        <v>59</v>
       </c>
       <c r="C6">
         <v>1</v>
       </c>
       <c r="D6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E6" t="s">
         <v>45</v>
@@ -1788,39 +1765,39 @@
         <v>46</v>
       </c>
       <c r="H6" t="s">
+        <v>47</v>
+      </c>
+      <c r="I6" t="s">
+        <v>46</v>
+      </c>
+      <c r="J6" t="s">
+        <v>60</v>
+      </c>
+      <c r="K6" t="s">
         <v>61</v>
       </c>
-      <c r="I6" t="s">
-        <v>46</v>
-      </c>
-      <c r="J6" t="s">
+      <c r="L6" t="s">
+        <v>46</v>
+      </c>
+      <c r="M6" t="s">
         <v>62</v>
       </c>
-      <c r="K6" t="s">
-        <v>63</v>
-      </c>
-      <c r="L6" t="s">
-        <v>46</v>
-      </c>
-      <c r="M6" t="s">
-        <v>64</v>
-      </c>
       <c r="N6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="7" spans="1:14">
       <c r="A7" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C7">
         <v>1</v>
       </c>
       <c r="D7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E7" t="s">
         <v>45</v>
@@ -1832,39 +1809,39 @@
         <v>46</v>
       </c>
       <c r="H7" t="s">
+        <v>47</v>
+      </c>
+      <c r="I7" t="s">
+        <v>46</v>
+      </c>
+      <c r="J7" t="s">
+        <v>64</v>
+      </c>
+      <c r="K7" t="s">
+        <v>65</v>
+      </c>
+      <c r="L7" t="s">
+        <v>46</v>
+      </c>
+      <c r="M7" t="s">
         <v>66</v>
       </c>
-      <c r="I7" t="s">
-        <v>46</v>
-      </c>
-      <c r="J7" t="s">
+      <c r="N7" t="s">
         <v>67</v>
-      </c>
-      <c r="K7" t="s">
-        <v>68</v>
-      </c>
-      <c r="L7" t="s">
-        <v>46</v>
-      </c>
-      <c r="M7" t="s">
-        <v>69</v>
-      </c>
-      <c r="N7" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="8" spans="1:14">
       <c r="A8" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C8">
         <v>1</v>
       </c>
       <c r="D8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E8" t="s">
         <v>45</v>
@@ -1876,22 +1853,22 @@
         <v>46</v>
       </c>
       <c r="H8" t="s">
-        <v>66</v>
+        <v>47</v>
       </c>
       <c r="I8" t="s">
         <v>46</v>
       </c>
       <c r="J8" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="K8" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="L8" t="s">
         <v>46</v>
       </c>
       <c r="M8" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="N8" t="s">
         <v>51</v>
@@ -1899,16 +1876,16 @@
     </row>
     <row r="9" spans="1:14">
       <c r="A9" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C9">
         <v>1</v>
       </c>
       <c r="D9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E9" t="s">
         <v>45</v>
@@ -1920,39 +1897,39 @@
         <v>46</v>
       </c>
       <c r="H9" t="s">
-        <v>66</v>
+        <v>47</v>
       </c>
       <c r="I9" t="s">
         <v>46</v>
       </c>
       <c r="J9" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="K9" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="L9" t="s">
         <v>46</v>
       </c>
       <c r="M9" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="N9" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="10" spans="1:14">
       <c r="A10" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C10">
         <v>1</v>
       </c>
       <c r="D10" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E10" t="s">
         <v>45</v>
@@ -1964,7 +1941,7 @@
         <v>46</v>
       </c>
       <c r="H10" t="s">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="I10" t="s">
         <v>46</v>
@@ -1973,7 +1950,7 @@
         <v>48</v>
       </c>
       <c r="K10" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="L10" t="s">
         <v>50</v>
@@ -1982,21 +1959,21 @@
         <v>48</v>
       </c>
       <c r="N10" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="11" spans="1:14">
       <c r="A11" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="B11" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C11">
         <v>1</v>
       </c>
       <c r="D11" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="E11" t="s">
         <v>45</v>
@@ -2008,7 +1985,7 @@
         <v>46</v>
       </c>
       <c r="H11" t="s">
-        <v>85</v>
+        <v>47</v>
       </c>
       <c r="I11" t="s">
         <v>46</v>
@@ -2017,7 +1994,7 @@
         <v>48</v>
       </c>
       <c r="K11" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="L11" t="s">
         <v>50</v>
@@ -2026,12 +2003,12 @@
         <v>48</v>
       </c>
       <c r="N11" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="12" spans="1:14">
       <c r="A12" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="B12" t="s">
         <v>43</v>
@@ -2052,7 +2029,7 @@
         <v>46</v>
       </c>
       <c r="H12" t="s">
-        <v>47</v>
+        <v>83</v>
       </c>
       <c r="I12" t="s">
         <v>46</v>
@@ -2075,7 +2052,7 @@
     </row>
     <row r="13" spans="1:14">
       <c r="A13" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B13" t="s">
         <v>53</v>
@@ -2096,16 +2073,16 @@
         <v>46</v>
       </c>
       <c r="H13" t="s">
+        <v>83</v>
+      </c>
+      <c r="I13" t="s">
+        <v>46</v>
+      </c>
+      <c r="J13" t="s">
+        <v>48</v>
+      </c>
+      <c r="K13" t="s">
         <v>55</v>
-      </c>
-      <c r="I13" t="s">
-        <v>46</v>
-      </c>
-      <c r="J13" t="s">
-        <v>48</v>
-      </c>
-      <c r="K13" t="s">
-        <v>56</v>
       </c>
       <c r="L13" t="s">
         <v>50</v>
@@ -2114,21 +2091,21 @@
         <v>48</v>
       </c>
       <c r="N13" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="14" spans="1:14">
       <c r="A14" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="B14" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C14">
         <v>2</v>
       </c>
       <c r="D14" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E14" t="s">
         <v>45</v>
@@ -2140,39 +2117,39 @@
         <v>46</v>
       </c>
       <c r="H14" t="s">
+        <v>83</v>
+      </c>
+      <c r="I14" t="s">
+        <v>46</v>
+      </c>
+      <c r="J14" t="s">
+        <v>60</v>
+      </c>
+      <c r="K14" t="s">
         <v>61</v>
       </c>
-      <c r="I14" t="s">
-        <v>46</v>
-      </c>
-      <c r="J14" t="s">
-        <v>62</v>
-      </c>
-      <c r="K14" t="s">
-        <v>63</v>
-      </c>
       <c r="L14" t="s">
         <v>46</v>
       </c>
       <c r="M14" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="N14" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="B15" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C15">
         <v>2</v>
       </c>
       <c r="D15" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E15" t="s">
         <v>45</v>
@@ -2184,39 +2161,39 @@
         <v>46</v>
       </c>
       <c r="H15" t="s">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="I15" t="s">
         <v>46</v>
       </c>
       <c r="J15" t="s">
+        <v>64</v>
+      </c>
+      <c r="K15" t="s">
+        <v>65</v>
+      </c>
+      <c r="L15" t="s">
+        <v>46</v>
+      </c>
+      <c r="M15" t="s">
+        <v>88</v>
+      </c>
+      <c r="N15" t="s">
         <v>67</v>
-      </c>
-      <c r="K15" t="s">
-        <v>68</v>
-      </c>
-      <c r="L15" t="s">
-        <v>46</v>
-      </c>
-      <c r="M15" t="s">
-        <v>92</v>
-      </c>
-      <c r="N15" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="B16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C16">
         <v>2</v>
       </c>
       <c r="D16" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E16" t="s">
         <v>45</v>
@@ -2228,22 +2205,22 @@
         <v>46</v>
       </c>
       <c r="H16" t="s">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="I16" t="s">
         <v>46</v>
       </c>
       <c r="J16" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="K16" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="L16" t="s">
         <v>46</v>
       </c>
       <c r="M16" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="N16" t="s">
         <v>51</v>
@@ -2251,16 +2228,16 @@
     </row>
     <row r="17" spans="1:14">
       <c r="A17" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="B17" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C17">
         <v>2</v>
       </c>
       <c r="D17" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E17" t="s">
         <v>45</v>
@@ -2272,39 +2249,39 @@
         <v>46</v>
       </c>
       <c r="H17" t="s">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="I17" t="s">
         <v>46</v>
       </c>
       <c r="J17" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="K17" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="L17" t="s">
         <v>46</v>
       </c>
       <c r="M17" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="N17" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="B18" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C18">
         <v>3</v>
       </c>
       <c r="D18" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E18" t="s">
         <v>45</v>
@@ -2316,39 +2293,39 @@
         <v>46</v>
       </c>
       <c r="H18" t="s">
-        <v>66</v>
+        <v>94</v>
       </c>
       <c r="I18" t="s">
         <v>46</v>
       </c>
       <c r="J18" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="K18" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="L18" t="s">
         <v>46</v>
       </c>
       <c r="M18" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="N18" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B19" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C19">
         <v>3</v>
       </c>
       <c r="D19" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E19" t="s">
         <v>45</v>
@@ -2360,39 +2337,39 @@
         <v>46</v>
       </c>
       <c r="H19" t="s">
-        <v>66</v>
+        <v>94</v>
       </c>
       <c r="I19" t="s">
         <v>46</v>
       </c>
       <c r="J19" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="K19" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="L19" t="s">
         <v>46</v>
       </c>
       <c r="M19" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="N19" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B20" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C20">
         <v>3</v>
       </c>
       <c r="D20" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E20" t="s">
         <v>45</v>
@@ -2404,22 +2381,22 @@
         <v>46</v>
       </c>
       <c r="H20" t="s">
-        <v>66</v>
+        <v>94</v>
       </c>
       <c r="I20" t="s">
         <v>46</v>
       </c>
       <c r="J20" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="K20" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="L20" t="s">
         <v>46</v>
       </c>
       <c r="M20" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="N20" t="s">
         <v>51</v>
@@ -2427,16 +2404,16 @@
     </row>
     <row r="21" spans="1:14">
       <c r="A21" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B21" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C21">
         <v>3</v>
       </c>
       <c r="D21" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E21" t="s">
         <v>45</v>
@@ -2448,39 +2425,39 @@
         <v>46</v>
       </c>
       <c r="H21" t="s">
-        <v>66</v>
+        <v>94</v>
       </c>
       <c r="I21" t="s">
         <v>46</v>
       </c>
       <c r="J21" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="K21" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="L21" t="s">
         <v>46</v>
       </c>
       <c r="M21" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="N21" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B22" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C22">
         <v>3</v>
       </c>
       <c r="D22" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E22" t="s">
         <v>45</v>
@@ -2492,39 +2469,39 @@
         <v>46</v>
       </c>
       <c r="H22" t="s">
-        <v>66</v>
+        <v>94</v>
       </c>
       <c r="I22" t="s">
         <v>46</v>
       </c>
       <c r="J22" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="K22" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="L22" t="s">
         <v>46</v>
       </c>
       <c r="M22" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="N22" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="23" spans="1:14">
       <c r="A23" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B23" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C23">
         <v>3</v>
       </c>
       <c r="D23" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E23" t="s">
         <v>45</v>
@@ -2536,39 +2513,39 @@
         <v>46</v>
       </c>
       <c r="H23" t="s">
-        <v>66</v>
+        <v>94</v>
       </c>
       <c r="I23" t="s">
         <v>46</v>
       </c>
       <c r="J23" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="K23" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="L23" t="s">
         <v>46</v>
       </c>
       <c r="M23" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="N23" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="24" spans="1:14">
       <c r="A24" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="B24" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C24">
         <v>3</v>
       </c>
       <c r="D24" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E24" t="s">
         <v>45</v>
@@ -2580,22 +2557,22 @@
         <v>46</v>
       </c>
       <c r="H24" t="s">
-        <v>122</v>
+        <v>94</v>
       </c>
       <c r="I24" t="s">
         <v>46</v>
       </c>
       <c r="J24" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="K24" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="L24" t="s">
         <v>46</v>
       </c>
       <c r="M24" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="N24" t="s">
         <v>51</v>
@@ -2603,16 +2580,16 @@
     </row>
     <row r="25" spans="1:14">
       <c r="A25" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="B25" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C25">
         <v>3</v>
       </c>
       <c r="D25" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E25" t="s">
         <v>45</v>
@@ -2624,22 +2601,22 @@
         <v>46</v>
       </c>
       <c r="H25" t="s">
-        <v>127</v>
+        <v>94</v>
       </c>
       <c r="I25" t="s">
         <v>46</v>
       </c>
       <c r="J25" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="K25" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="L25" t="s">
         <v>46</v>
       </c>
       <c r="M25" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="N25" t="s">
         <v>51</v>
@@ -2647,19 +2624,19 @@
     </row>
     <row r="26" spans="1:14">
       <c r="A26" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="B26" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="C26">
         <v>4</v>
       </c>
       <c r="D26" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E26" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="F26" t="s">
         <v>46</v>
@@ -2668,42 +2645,42 @@
         <v>46</v>
       </c>
       <c r="H26" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="I26" t="s">
         <v>46</v>
       </c>
       <c r="J26" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="K26" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="L26" t="s">
         <v>46</v>
       </c>
       <c r="M26" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="N26" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="B27" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="C27">
         <v>4</v>
       </c>
       <c r="D27" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E27" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="F27" t="s">
         <v>46</v>
@@ -2712,22 +2689,22 @@
         <v>46</v>
       </c>
       <c r="H27" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
       <c r="I27" t="s">
         <v>46</v>
       </c>
       <c r="J27" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="K27" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="L27" t="s">
         <v>46</v>
       </c>
       <c r="M27" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="N27" t="s">
         <v>51</v>
@@ -2735,16 +2712,16 @@
     </row>
     <row r="28" spans="1:14">
       <c r="A28" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="B28" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C28">
         <v>2</v>
       </c>
       <c r="D28" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E28" t="s">
         <v>45</v>
@@ -2756,7 +2733,7 @@
         <v>46</v>
       </c>
       <c r="H28" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="I28" t="s">
         <v>46</v>
@@ -2765,7 +2742,7 @@
         <v>48</v>
       </c>
       <c r="K28" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="L28" t="s">
         <v>50</v>
@@ -2774,21 +2751,21 @@
         <v>48</v>
       </c>
       <c r="N28" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="B29" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C29">
         <v>2</v>
       </c>
       <c r="D29" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="E29" t="s">
         <v>45</v>
@@ -2800,7 +2777,7 @@
         <v>46</v>
       </c>
       <c r="H29" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="I29" t="s">
         <v>46</v>
@@ -2809,7 +2786,7 @@
         <v>48</v>
       </c>
       <c r="K29" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="L29" t="s">
         <v>50</v>
@@ -2818,12 +2795,12 @@
         <v>48</v>
       </c>
       <c r="N29" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="B30" t="s">
         <v>43</v>
@@ -2844,7 +2821,7 @@
         <v>46</v>
       </c>
       <c r="H30" t="s">
-        <v>148</v>
+        <v>94</v>
       </c>
       <c r="I30" t="s">
         <v>46</v>
@@ -2853,7 +2830,7 @@
         <v>48</v>
       </c>
       <c r="K30" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="L30" t="s">
         <v>50</v>
@@ -2862,12 +2839,12 @@
         <v>48</v>
       </c>
       <c r="N30" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="B31" t="s">
         <v>53</v>
@@ -2888,7 +2865,7 @@
         <v>46</v>
       </c>
       <c r="H31" t="s">
-        <v>151</v>
+        <v>94</v>
       </c>
       <c r="I31" t="s">
         <v>46</v>
@@ -2897,7 +2874,7 @@
         <v>48</v>
       </c>
       <c r="K31" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="L31" t="s">
         <v>50</v>
@@ -2906,21 +2883,21 @@
         <v>48</v>
       </c>
       <c r="N31" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="32" spans="1:14">
       <c r="A32" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="B32" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C32">
         <v>3</v>
       </c>
       <c r="D32" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E32" t="s">
         <v>45</v>
@@ -2932,7 +2909,7 @@
         <v>46</v>
       </c>
       <c r="H32" t="s">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="I32" t="s">
         <v>46</v>
@@ -2941,7 +2918,7 @@
         <v>48</v>
       </c>
       <c r="K32" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="L32" t="s">
         <v>50</v>
@@ -2950,21 +2927,21 @@
         <v>48</v>
       </c>
       <c r="N32" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="33" spans="1:14">
       <c r="A33" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="B33" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C33">
         <v>3</v>
       </c>
       <c r="D33" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="E33" t="s">
         <v>45</v>
@@ -2976,7 +2953,7 @@
         <v>46</v>
       </c>
       <c r="H33" t="s">
-        <v>151</v>
+        <v>94</v>
       </c>
       <c r="I33" t="s">
         <v>46</v>
@@ -2985,7 +2962,7 @@
         <v>48</v>
       </c>
       <c r="K33" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="L33" t="s">
         <v>50</v>
@@ -2999,10 +2976,10 @@
     </row>
     <row r="34" spans="1:14">
       <c r="A34" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="B34" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="C34">
         <v>4</v>
@@ -3011,7 +2988,7 @@
         <v>44</v>
       </c>
       <c r="E34" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="F34" t="s">
         <v>46</v>
@@ -3020,16 +2997,16 @@
         <v>46</v>
       </c>
       <c r="H34" t="s">
+        <v>129</v>
+      </c>
+      <c r="I34" t="s">
+        <v>46</v>
+      </c>
+      <c r="J34" t="s">
+        <v>48</v>
+      </c>
+      <c r="K34" t="s">
         <v>151</v>
-      </c>
-      <c r="I34" t="s">
-        <v>46</v>
-      </c>
-      <c r="J34" t="s">
-        <v>48</v>
-      </c>
-      <c r="K34" t="s">
-        <v>159</v>
       </c>
       <c r="L34" t="s">
         <v>50</v>
@@ -3038,15 +3015,15 @@
         <v>48</v>
       </c>
       <c r="N34" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="35" spans="1:14">
       <c r="A35" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="B35" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="C35">
         <v>4</v>
@@ -3055,7 +3032,7 @@
         <v>54</v>
       </c>
       <c r="E35" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="F35" t="s">
         <v>46</v>
@@ -3064,7 +3041,7 @@
         <v>46</v>
       </c>
       <c r="H35" t="s">
-        <v>151</v>
+        <v>129</v>
       </c>
       <c r="I35" t="s">
         <v>46</v>
@@ -3073,7 +3050,7 @@
         <v>48</v>
       </c>
       <c r="K35" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="L35" t="s">
         <v>50</v>
@@ -3082,24 +3059,24 @@
         <v>48</v>
       </c>
       <c r="N35" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="36" spans="1:14">
       <c r="A36" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="B36" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="C36">
         <v>4</v>
       </c>
       <c r="D36" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E36" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="F36" t="s">
         <v>46</v>
@@ -3108,7 +3085,7 @@
         <v>46</v>
       </c>
       <c r="H36" t="s">
-        <v>151</v>
+        <v>129</v>
       </c>
       <c r="I36" t="s">
         <v>46</v>
@@ -3117,7 +3094,7 @@
         <v>48</v>
       </c>
       <c r="K36" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="L36" t="s">
         <v>50</v>
@@ -3126,24 +3103,24 @@
         <v>48</v>
       </c>
       <c r="N36" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="37" spans="1:14">
       <c r="A37" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="B37" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="C37">
         <v>4</v>
       </c>
       <c r="D37" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="E37" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="F37" t="s">
         <v>46</v>
@@ -3152,7 +3129,7 @@
         <v>46</v>
       </c>
       <c r="H37" t="s">
-        <v>151</v>
+        <v>129</v>
       </c>
       <c r="I37" t="s">
         <v>46</v>
@@ -3161,7 +3138,7 @@
         <v>48</v>
       </c>
       <c r="K37" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="L37" t="s">
         <v>50</v>
@@ -3170,15 +3147,15 @@
         <v>48</v>
       </c>
       <c r="N37" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="38" spans="1:14">
       <c r="A38" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="B38" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="C38">
         <v>4</v>
@@ -3187,7 +3164,7 @@
         <v>44</v>
       </c>
       <c r="E38" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="F38" t="s">
         <v>46</v>
@@ -3196,7 +3173,7 @@
         <v>46</v>
       </c>
       <c r="H38" t="s">
-        <v>151</v>
+        <v>129</v>
       </c>
       <c r="I38" t="s">
         <v>46</v>
@@ -3205,7 +3182,7 @@
         <v>48</v>
       </c>
       <c r="K38" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="L38" t="s">
         <v>50</v>
@@ -3214,15 +3191,15 @@
         <v>48</v>
       </c>
       <c r="N38" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="39" spans="1:14">
       <c r="A39" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="B39" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="C39">
         <v>4</v>
@@ -3231,7 +3208,7 @@
         <v>54</v>
       </c>
       <c r="E39" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="F39" t="s">
         <v>46</v>
@@ -3240,7 +3217,7 @@
         <v>46</v>
       </c>
       <c r="H39" t="s">
-        <v>151</v>
+        <v>129</v>
       </c>
       <c r="I39" t="s">
         <v>46</v>
@@ -3249,7 +3226,7 @@
         <v>48</v>
       </c>
       <c r="K39" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="L39" t="s">
         <v>50</v>
@@ -3258,24 +3235,24 @@
         <v>48</v>
       </c>
       <c r="N39" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="40" spans="1:14">
       <c r="A40" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="B40" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="C40">
         <v>4</v>
       </c>
       <c r="D40" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E40" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="F40" t="s">
         <v>46</v>
@@ -3284,7 +3261,7 @@
         <v>46</v>
       </c>
       <c r="H40" t="s">
-        <v>151</v>
+        <v>129</v>
       </c>
       <c r="I40" t="s">
         <v>46</v>
@@ -3293,7 +3270,7 @@
         <v>48</v>
       </c>
       <c r="K40" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="L40" t="s">
         <v>50</v>
@@ -3307,19 +3284,19 @@
     </row>
     <row r="41" spans="1:14">
       <c r="A41" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="B41" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="C41">
         <v>4</v>
       </c>
       <c r="D41" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="E41" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="F41" t="s">
         <v>46</v>
@@ -3328,7 +3305,7 @@
         <v>46</v>
       </c>
       <c r="H41" t="s">
-        <v>151</v>
+        <v>129</v>
       </c>
       <c r="I41" t="s">
         <v>46</v>
@@ -3337,7 +3314,7 @@
         <v>48</v>
       </c>
       <c r="K41" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="L41" t="s">
         <v>50</v>
@@ -3346,7 +3323,7 @@
         <v>48</v>
       </c>
       <c r="N41" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>

--- a/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/制造_躯体材料配置表_Manufacture_BodyPartConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/制造_躯体材料配置表_Manufacture_BodyPartConfig.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="536" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1004" uniqueCount="234">
   <si>
     <t>躯体ID</t>
   </si>
@@ -545,6 +545,195 @@
   </si>
   <si>
     <t>Art_BP_Leg_Demon</t>
+  </si>
+  <si>
+    <t>BP_Arm_Human_Guardian</t>
+  </si>
+  <si>
+    <t>人类手臂</t>
+  </si>
+  <si>
+    <t>Race_Human</t>
+  </si>
+  <si>
+    <t>BP_Arm_Human_BombMaster</t>
+  </si>
+  <si>
+    <t>BP_Arm_Human_IceMage</t>
+  </si>
+  <si>
+    <t>BP_Arm_Human_Brawler</t>
+  </si>
+  <si>
+    <t>BP_Arm_Human_Berserker</t>
+  </si>
+  <si>
+    <t>BP_Arm_Human_Longbowman</t>
+  </si>
+  <si>
+    <t>BP_Arm_Human_FireMage</t>
+  </si>
+  <si>
+    <t>BP_Arm_Human_Shadowblade</t>
+  </si>
+  <si>
+    <t>BP_Head_Human_2</t>
+  </si>
+  <si>
+    <t>人类头部</t>
+  </si>
+  <si>
+    <t>Art_BP_Head_Human_2</t>
+  </si>
+  <si>
+    <t>BP_Torso_Human_2</t>
+  </si>
+  <si>
+    <t>人类躯干</t>
+  </si>
+  <si>
+    <t>Art_BP_Torso_Human_2</t>
+  </si>
+  <si>
+    <t>BP_Arm_Human_2</t>
+  </si>
+  <si>
+    <t>Art_BP_Arm_Human_2</t>
+  </si>
+  <si>
+    <t>BP_Leg_Human_2</t>
+  </si>
+  <si>
+    <t>人类腿部</t>
+  </si>
+  <si>
+    <t>Art_BP_Leg_Human_2</t>
+  </si>
+  <si>
+    <t>BP_Arm_Elf_Guardian</t>
+  </si>
+  <si>
+    <t>精灵手臂</t>
+  </si>
+  <si>
+    <t>Race_Elf</t>
+  </si>
+  <si>
+    <t>BP_Arm_Elf_BombMaster</t>
+  </si>
+  <si>
+    <t>BP_Arm_Elf_IceMage</t>
+  </si>
+  <si>
+    <t>BP_Arm_Elf_Brawler</t>
+  </si>
+  <si>
+    <t>BP_Arm_Elf_Berserker</t>
+  </si>
+  <si>
+    <t>BP_Arm_Elf_Longbowman</t>
+  </si>
+  <si>
+    <t>BP_Arm_Elf_FireMage</t>
+  </si>
+  <si>
+    <t>BP_Arm_Elf_Shadowblade</t>
+  </si>
+  <si>
+    <t>BP_Head_Elf_2</t>
+  </si>
+  <si>
+    <t>精灵头部</t>
+  </si>
+  <si>
+    <t>Art_BP_Head_Elf_2</t>
+  </si>
+  <si>
+    <t>BP_Torso_Elf_2</t>
+  </si>
+  <si>
+    <t>精灵躯干</t>
+  </si>
+  <si>
+    <t>Art_BP_Torso_Elf_2</t>
+  </si>
+  <si>
+    <t>BP_Arm_Elf_2</t>
+  </si>
+  <si>
+    <t>Art_BP_Arm_Elf_2</t>
+  </si>
+  <si>
+    <t>BP_Leg_Elf_2</t>
+  </si>
+  <si>
+    <t>精灵腿部</t>
+  </si>
+  <si>
+    <t>Art_BP_Leg_Elf_2</t>
+  </si>
+  <si>
+    <t>BP_Arm_Orc_Guardian</t>
+  </si>
+  <si>
+    <t>兽人手臂</t>
+  </si>
+  <si>
+    <t>Race_Orc</t>
+  </si>
+  <si>
+    <t>BP_Arm_Orc_BombMaster</t>
+  </si>
+  <si>
+    <t>BP_Arm_Orc_IceMage</t>
+  </si>
+  <si>
+    <t>BP_Arm_Orc_Brawler</t>
+  </si>
+  <si>
+    <t>BP_Arm_Orc_Berserker</t>
+  </si>
+  <si>
+    <t>BP_Arm_Orc_Longbowman</t>
+  </si>
+  <si>
+    <t>BP_Arm_Orc_FireMage</t>
+  </si>
+  <si>
+    <t>BP_Arm_Orc_Shadowblade</t>
+  </si>
+  <si>
+    <t>BP_Head_Orc_2</t>
+  </si>
+  <si>
+    <t>兽人头部</t>
+  </si>
+  <si>
+    <t>Art_BP_Head_Orc_2</t>
+  </si>
+  <si>
+    <t>BP_Torso_Orc_2</t>
+  </si>
+  <si>
+    <t>兽人躯干</t>
+  </si>
+  <si>
+    <t>Art_BP_Torso_Orc_2</t>
+  </si>
+  <si>
+    <t>BP_Arm_Orc_2</t>
+  </si>
+  <si>
+    <t>Art_BP_Arm_Orc_2</t>
+  </si>
+  <si>
+    <t>BP_Leg_Orc_2</t>
+  </si>
+  <si>
+    <t>兽人腿部</t>
+  </si>
+  <si>
+    <t>Art_BP_Leg_Orc_2</t>
   </si>
 </sst>
 </file>
@@ -1513,7 +1702,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N41"/>
+  <dimension ref="A1:N77"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="24.625" customWidth="1"/>
@@ -3326,6 +3515,1590 @@
         <v>67</v>
       </c>
     </row>
+    <row r="42" spans="1:14">
+      <c r="A42" t="s">
+        <v>171</v>
+      </c>
+      <c r="B42" t="s">
+        <v>172</v>
+      </c>
+      <c r="C42">
+        <v>3</v>
+      </c>
+      <c r="D42" t="s">
+        <v>59</v>
+      </c>
+      <c r="E42" t="s">
+        <v>173</v>
+      </c>
+      <c r="F42" t="s">
+        <v>46</v>
+      </c>
+      <c r="G42" t="s">
+        <v>46</v>
+      </c>
+      <c r="H42" t="s">
+        <v>94</v>
+      </c>
+      <c r="I42" t="s">
+        <v>46</v>
+      </c>
+      <c r="J42" t="s">
+        <v>95</v>
+      </c>
+      <c r="K42" t="s">
+        <v>96</v>
+      </c>
+      <c r="L42" t="s">
+        <v>46</v>
+      </c>
+      <c r="M42" t="s">
+        <v>97</v>
+      </c>
+      <c r="N42" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14">
+      <c r="A43" t="s">
+        <v>174</v>
+      </c>
+      <c r="B43" t="s">
+        <v>172</v>
+      </c>
+      <c r="C43">
+        <v>3</v>
+      </c>
+      <c r="D43" t="s">
+        <v>59</v>
+      </c>
+      <c r="E43" t="s">
+        <v>173</v>
+      </c>
+      <c r="F43" t="s">
+        <v>46</v>
+      </c>
+      <c r="G43" t="s">
+        <v>46</v>
+      </c>
+      <c r="H43" t="s">
+        <v>94</v>
+      </c>
+      <c r="I43" t="s">
+        <v>46</v>
+      </c>
+      <c r="J43" t="s">
+        <v>99</v>
+      </c>
+      <c r="K43" t="s">
+        <v>100</v>
+      </c>
+      <c r="L43" t="s">
+        <v>46</v>
+      </c>
+      <c r="M43" t="s">
+        <v>101</v>
+      </c>
+      <c r="N43" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14">
+      <c r="A44" t="s">
+        <v>175</v>
+      </c>
+      <c r="B44" t="s">
+        <v>172</v>
+      </c>
+      <c r="C44">
+        <v>3</v>
+      </c>
+      <c r="D44" t="s">
+        <v>59</v>
+      </c>
+      <c r="E44" t="s">
+        <v>173</v>
+      </c>
+      <c r="F44" t="s">
+        <v>46</v>
+      </c>
+      <c r="G44" t="s">
+        <v>46</v>
+      </c>
+      <c r="H44" t="s">
+        <v>94</v>
+      </c>
+      <c r="I44" t="s">
+        <v>46</v>
+      </c>
+      <c r="J44" t="s">
+        <v>103</v>
+      </c>
+      <c r="K44" t="s">
+        <v>104</v>
+      </c>
+      <c r="L44" t="s">
+        <v>46</v>
+      </c>
+      <c r="M44" t="s">
+        <v>105</v>
+      </c>
+      <c r="N44" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14">
+      <c r="A45" t="s">
+        <v>176</v>
+      </c>
+      <c r="B45" t="s">
+        <v>172</v>
+      </c>
+      <c r="C45">
+        <v>3</v>
+      </c>
+      <c r="D45" t="s">
+        <v>59</v>
+      </c>
+      <c r="E45" t="s">
+        <v>173</v>
+      </c>
+      <c r="F45" t="s">
+        <v>46</v>
+      </c>
+      <c r="G45" t="s">
+        <v>46</v>
+      </c>
+      <c r="H45" t="s">
+        <v>94</v>
+      </c>
+      <c r="I45" t="s">
+        <v>46</v>
+      </c>
+      <c r="J45" t="s">
+        <v>107</v>
+      </c>
+      <c r="K45" t="s">
+        <v>108</v>
+      </c>
+      <c r="L45" t="s">
+        <v>46</v>
+      </c>
+      <c r="M45" t="s">
+        <v>109</v>
+      </c>
+      <c r="N45" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14">
+      <c r="A46" t="s">
+        <v>177</v>
+      </c>
+      <c r="B46" t="s">
+        <v>172</v>
+      </c>
+      <c r="C46">
+        <v>3</v>
+      </c>
+      <c r="D46" t="s">
+        <v>59</v>
+      </c>
+      <c r="E46" t="s">
+        <v>173</v>
+      </c>
+      <c r="F46" t="s">
+        <v>46</v>
+      </c>
+      <c r="G46" t="s">
+        <v>46</v>
+      </c>
+      <c r="H46" t="s">
+        <v>94</v>
+      </c>
+      <c r="I46" t="s">
+        <v>46</v>
+      </c>
+      <c r="J46" t="s">
+        <v>111</v>
+      </c>
+      <c r="K46" t="s">
+        <v>112</v>
+      </c>
+      <c r="L46" t="s">
+        <v>46</v>
+      </c>
+      <c r="M46" t="s">
+        <v>113</v>
+      </c>
+      <c r="N46" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14">
+      <c r="A47" t="s">
+        <v>178</v>
+      </c>
+      <c r="B47" t="s">
+        <v>172</v>
+      </c>
+      <c r="C47">
+        <v>3</v>
+      </c>
+      <c r="D47" t="s">
+        <v>59</v>
+      </c>
+      <c r="E47" t="s">
+        <v>173</v>
+      </c>
+      <c r="F47" t="s">
+        <v>46</v>
+      </c>
+      <c r="G47" t="s">
+        <v>46</v>
+      </c>
+      <c r="H47" t="s">
+        <v>94</v>
+      </c>
+      <c r="I47" t="s">
+        <v>46</v>
+      </c>
+      <c r="J47" t="s">
+        <v>115</v>
+      </c>
+      <c r="K47" t="s">
+        <v>116</v>
+      </c>
+      <c r="L47" t="s">
+        <v>46</v>
+      </c>
+      <c r="M47" t="s">
+        <v>117</v>
+      </c>
+      <c r="N47" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14">
+      <c r="A48" t="s">
+        <v>179</v>
+      </c>
+      <c r="B48" t="s">
+        <v>172</v>
+      </c>
+      <c r="C48">
+        <v>3</v>
+      </c>
+      <c r="D48" t="s">
+        <v>59</v>
+      </c>
+      <c r="E48" t="s">
+        <v>173</v>
+      </c>
+      <c r="F48" t="s">
+        <v>46</v>
+      </c>
+      <c r="G48" t="s">
+        <v>46</v>
+      </c>
+      <c r="H48" t="s">
+        <v>94</v>
+      </c>
+      <c r="I48" t="s">
+        <v>46</v>
+      </c>
+      <c r="J48" t="s">
+        <v>119</v>
+      </c>
+      <c r="K48" t="s">
+        <v>120</v>
+      </c>
+      <c r="L48" t="s">
+        <v>46</v>
+      </c>
+      <c r="M48" t="s">
+        <v>121</v>
+      </c>
+      <c r="N48" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14">
+      <c r="A49" t="s">
+        <v>180</v>
+      </c>
+      <c r="B49" t="s">
+        <v>172</v>
+      </c>
+      <c r="C49">
+        <v>3</v>
+      </c>
+      <c r="D49" t="s">
+        <v>59</v>
+      </c>
+      <c r="E49" t="s">
+        <v>173</v>
+      </c>
+      <c r="F49" t="s">
+        <v>46</v>
+      </c>
+      <c r="G49" t="s">
+        <v>46</v>
+      </c>
+      <c r="H49" t="s">
+        <v>94</v>
+      </c>
+      <c r="I49" t="s">
+        <v>46</v>
+      </c>
+      <c r="J49" t="s">
+        <v>123</v>
+      </c>
+      <c r="K49" t="s">
+        <v>124</v>
+      </c>
+      <c r="L49" t="s">
+        <v>46</v>
+      </c>
+      <c r="M49" t="s">
+        <v>125</v>
+      </c>
+      <c r="N49" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14">
+      <c r="A50" t="s">
+        <v>181</v>
+      </c>
+      <c r="B50" t="s">
+        <v>182</v>
+      </c>
+      <c r="C50">
+        <v>3</v>
+      </c>
+      <c r="D50" t="s">
+        <v>44</v>
+      </c>
+      <c r="E50" t="s">
+        <v>173</v>
+      </c>
+      <c r="F50" t="s">
+        <v>46</v>
+      </c>
+      <c r="G50" t="s">
+        <v>46</v>
+      </c>
+      <c r="H50" t="s">
+        <v>94</v>
+      </c>
+      <c r="I50" t="s">
+        <v>46</v>
+      </c>
+      <c r="J50" t="s">
+        <v>48</v>
+      </c>
+      <c r="K50" t="s">
+        <v>183</v>
+      </c>
+      <c r="L50" t="s">
+        <v>50</v>
+      </c>
+      <c r="M50" t="s">
+        <v>48</v>
+      </c>
+      <c r="N50" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14">
+      <c r="A51" t="s">
+        <v>184</v>
+      </c>
+      <c r="B51" t="s">
+        <v>185</v>
+      </c>
+      <c r="C51">
+        <v>3</v>
+      </c>
+      <c r="D51" t="s">
+        <v>54</v>
+      </c>
+      <c r="E51" t="s">
+        <v>173</v>
+      </c>
+      <c r="F51" t="s">
+        <v>46</v>
+      </c>
+      <c r="G51" t="s">
+        <v>46</v>
+      </c>
+      <c r="H51" t="s">
+        <v>94</v>
+      </c>
+      <c r="I51" t="s">
+        <v>46</v>
+      </c>
+      <c r="J51" t="s">
+        <v>48</v>
+      </c>
+      <c r="K51" t="s">
+        <v>186</v>
+      </c>
+      <c r="L51" t="s">
+        <v>50</v>
+      </c>
+      <c r="M51" t="s">
+        <v>48</v>
+      </c>
+      <c r="N51" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14">
+      <c r="A52" t="s">
+        <v>187</v>
+      </c>
+      <c r="B52" t="s">
+        <v>172</v>
+      </c>
+      <c r="C52">
+        <v>3</v>
+      </c>
+      <c r="D52" t="s">
+        <v>59</v>
+      </c>
+      <c r="E52" t="s">
+        <v>173</v>
+      </c>
+      <c r="F52" t="s">
+        <v>46</v>
+      </c>
+      <c r="G52" t="s">
+        <v>46</v>
+      </c>
+      <c r="H52" t="s">
+        <v>94</v>
+      </c>
+      <c r="I52" t="s">
+        <v>46</v>
+      </c>
+      <c r="J52" t="s">
+        <v>48</v>
+      </c>
+      <c r="K52" t="s">
+        <v>188</v>
+      </c>
+      <c r="L52" t="s">
+        <v>50</v>
+      </c>
+      <c r="M52" t="s">
+        <v>48</v>
+      </c>
+      <c r="N52" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14">
+      <c r="A53" t="s">
+        <v>189</v>
+      </c>
+      <c r="B53" t="s">
+        <v>190</v>
+      </c>
+      <c r="C53">
+        <v>3</v>
+      </c>
+      <c r="D53" t="s">
+        <v>80</v>
+      </c>
+      <c r="E53" t="s">
+        <v>173</v>
+      </c>
+      <c r="F53" t="s">
+        <v>46</v>
+      </c>
+      <c r="G53" t="s">
+        <v>46</v>
+      </c>
+      <c r="H53" t="s">
+        <v>94</v>
+      </c>
+      <c r="I53" t="s">
+        <v>46</v>
+      </c>
+      <c r="J53" t="s">
+        <v>48</v>
+      </c>
+      <c r="K53" t="s">
+        <v>191</v>
+      </c>
+      <c r="L53" t="s">
+        <v>50</v>
+      </c>
+      <c r="M53" t="s">
+        <v>48</v>
+      </c>
+      <c r="N53" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14">
+      <c r="A54" t="s">
+        <v>192</v>
+      </c>
+      <c r="B54" t="s">
+        <v>193</v>
+      </c>
+      <c r="C54">
+        <v>3</v>
+      </c>
+      <c r="D54" t="s">
+        <v>59</v>
+      </c>
+      <c r="E54" t="s">
+        <v>194</v>
+      </c>
+      <c r="F54" t="s">
+        <v>46</v>
+      </c>
+      <c r="G54" t="s">
+        <v>46</v>
+      </c>
+      <c r="H54" t="s">
+        <v>94</v>
+      </c>
+      <c r="I54" t="s">
+        <v>46</v>
+      </c>
+      <c r="J54" t="s">
+        <v>95</v>
+      </c>
+      <c r="K54" t="s">
+        <v>96</v>
+      </c>
+      <c r="L54" t="s">
+        <v>46</v>
+      </c>
+      <c r="M54" t="s">
+        <v>97</v>
+      </c>
+      <c r="N54" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14">
+      <c r="A55" t="s">
+        <v>195</v>
+      </c>
+      <c r="B55" t="s">
+        <v>193</v>
+      </c>
+      <c r="C55">
+        <v>3</v>
+      </c>
+      <c r="D55" t="s">
+        <v>59</v>
+      </c>
+      <c r="E55" t="s">
+        <v>194</v>
+      </c>
+      <c r="F55" t="s">
+        <v>46</v>
+      </c>
+      <c r="G55" t="s">
+        <v>46</v>
+      </c>
+      <c r="H55" t="s">
+        <v>94</v>
+      </c>
+      <c r="I55" t="s">
+        <v>46</v>
+      </c>
+      <c r="J55" t="s">
+        <v>99</v>
+      </c>
+      <c r="K55" t="s">
+        <v>100</v>
+      </c>
+      <c r="L55" t="s">
+        <v>46</v>
+      </c>
+      <c r="M55" t="s">
+        <v>101</v>
+      </c>
+      <c r="N55" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14">
+      <c r="A56" t="s">
+        <v>196</v>
+      </c>
+      <c r="B56" t="s">
+        <v>193</v>
+      </c>
+      <c r="C56">
+        <v>3</v>
+      </c>
+      <c r="D56" t="s">
+        <v>59</v>
+      </c>
+      <c r="E56" t="s">
+        <v>194</v>
+      </c>
+      <c r="F56" t="s">
+        <v>46</v>
+      </c>
+      <c r="G56" t="s">
+        <v>46</v>
+      </c>
+      <c r="H56" t="s">
+        <v>94</v>
+      </c>
+      <c r="I56" t="s">
+        <v>46</v>
+      </c>
+      <c r="J56" t="s">
+        <v>103</v>
+      </c>
+      <c r="K56" t="s">
+        <v>104</v>
+      </c>
+      <c r="L56" t="s">
+        <v>46</v>
+      </c>
+      <c r="M56" t="s">
+        <v>105</v>
+      </c>
+      <c r="N56" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="57" spans="1:14">
+      <c r="A57" t="s">
+        <v>197</v>
+      </c>
+      <c r="B57" t="s">
+        <v>193</v>
+      </c>
+      <c r="C57">
+        <v>3</v>
+      </c>
+      <c r="D57" t="s">
+        <v>59</v>
+      </c>
+      <c r="E57" t="s">
+        <v>194</v>
+      </c>
+      <c r="F57" t="s">
+        <v>46</v>
+      </c>
+      <c r="G57" t="s">
+        <v>46</v>
+      </c>
+      <c r="H57" t="s">
+        <v>94</v>
+      </c>
+      <c r="I57" t="s">
+        <v>46</v>
+      </c>
+      <c r="J57" t="s">
+        <v>107</v>
+      </c>
+      <c r="K57" t="s">
+        <v>108</v>
+      </c>
+      <c r="L57" t="s">
+        <v>46</v>
+      </c>
+      <c r="M57" t="s">
+        <v>109</v>
+      </c>
+      <c r="N57" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="58" spans="1:14">
+      <c r="A58" t="s">
+        <v>198</v>
+      </c>
+      <c r="B58" t="s">
+        <v>193</v>
+      </c>
+      <c r="C58">
+        <v>3</v>
+      </c>
+      <c r="D58" t="s">
+        <v>59</v>
+      </c>
+      <c r="E58" t="s">
+        <v>194</v>
+      </c>
+      <c r="F58" t="s">
+        <v>46</v>
+      </c>
+      <c r="G58" t="s">
+        <v>46</v>
+      </c>
+      <c r="H58" t="s">
+        <v>94</v>
+      </c>
+      <c r="I58" t="s">
+        <v>46</v>
+      </c>
+      <c r="J58" t="s">
+        <v>111</v>
+      </c>
+      <c r="K58" t="s">
+        <v>112</v>
+      </c>
+      <c r="L58" t="s">
+        <v>46</v>
+      </c>
+      <c r="M58" t="s">
+        <v>113</v>
+      </c>
+      <c r="N58" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="59" spans="1:14">
+      <c r="A59" t="s">
+        <v>199</v>
+      </c>
+      <c r="B59" t="s">
+        <v>193</v>
+      </c>
+      <c r="C59">
+        <v>3</v>
+      </c>
+      <c r="D59" t="s">
+        <v>59</v>
+      </c>
+      <c r="E59" t="s">
+        <v>194</v>
+      </c>
+      <c r="F59" t="s">
+        <v>46</v>
+      </c>
+      <c r="G59" t="s">
+        <v>46</v>
+      </c>
+      <c r="H59" t="s">
+        <v>94</v>
+      </c>
+      <c r="I59" t="s">
+        <v>46</v>
+      </c>
+      <c r="J59" t="s">
+        <v>115</v>
+      </c>
+      <c r="K59" t="s">
+        <v>116</v>
+      </c>
+      <c r="L59" t="s">
+        <v>46</v>
+      </c>
+      <c r="M59" t="s">
+        <v>117</v>
+      </c>
+      <c r="N59" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="60" spans="1:14">
+      <c r="A60" t="s">
+        <v>200</v>
+      </c>
+      <c r="B60" t="s">
+        <v>193</v>
+      </c>
+      <c r="C60">
+        <v>3</v>
+      </c>
+      <c r="D60" t="s">
+        <v>59</v>
+      </c>
+      <c r="E60" t="s">
+        <v>194</v>
+      </c>
+      <c r="F60" t="s">
+        <v>46</v>
+      </c>
+      <c r="G60" t="s">
+        <v>46</v>
+      </c>
+      <c r="H60" t="s">
+        <v>94</v>
+      </c>
+      <c r="I60" t="s">
+        <v>46</v>
+      </c>
+      <c r="J60" t="s">
+        <v>119</v>
+      </c>
+      <c r="K60" t="s">
+        <v>120</v>
+      </c>
+      <c r="L60" t="s">
+        <v>46</v>
+      </c>
+      <c r="M60" t="s">
+        <v>121</v>
+      </c>
+      <c r="N60" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="61" spans="1:14">
+      <c r="A61" t="s">
+        <v>201</v>
+      </c>
+      <c r="B61" t="s">
+        <v>193</v>
+      </c>
+      <c r="C61">
+        <v>3</v>
+      </c>
+      <c r="D61" t="s">
+        <v>59</v>
+      </c>
+      <c r="E61" t="s">
+        <v>194</v>
+      </c>
+      <c r="F61" t="s">
+        <v>46</v>
+      </c>
+      <c r="G61" t="s">
+        <v>46</v>
+      </c>
+      <c r="H61" t="s">
+        <v>94</v>
+      </c>
+      <c r="I61" t="s">
+        <v>46</v>
+      </c>
+      <c r="J61" t="s">
+        <v>123</v>
+      </c>
+      <c r="K61" t="s">
+        <v>124</v>
+      </c>
+      <c r="L61" t="s">
+        <v>46</v>
+      </c>
+      <c r="M61" t="s">
+        <v>125</v>
+      </c>
+      <c r="N61" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="62" spans="1:14">
+      <c r="A62" t="s">
+        <v>202</v>
+      </c>
+      <c r="B62" t="s">
+        <v>203</v>
+      </c>
+      <c r="C62">
+        <v>3</v>
+      </c>
+      <c r="D62" t="s">
+        <v>44</v>
+      </c>
+      <c r="E62" t="s">
+        <v>194</v>
+      </c>
+      <c r="F62" t="s">
+        <v>46</v>
+      </c>
+      <c r="G62" t="s">
+        <v>46</v>
+      </c>
+      <c r="H62" t="s">
+        <v>94</v>
+      </c>
+      <c r="I62" t="s">
+        <v>46</v>
+      </c>
+      <c r="J62" t="s">
+        <v>48</v>
+      </c>
+      <c r="K62" t="s">
+        <v>204</v>
+      </c>
+      <c r="L62" t="s">
+        <v>50</v>
+      </c>
+      <c r="M62" t="s">
+        <v>48</v>
+      </c>
+      <c r="N62" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="63" spans="1:14">
+      <c r="A63" t="s">
+        <v>205</v>
+      </c>
+      <c r="B63" t="s">
+        <v>206</v>
+      </c>
+      <c r="C63">
+        <v>3</v>
+      </c>
+      <c r="D63" t="s">
+        <v>54</v>
+      </c>
+      <c r="E63" t="s">
+        <v>194</v>
+      </c>
+      <c r="F63" t="s">
+        <v>46</v>
+      </c>
+      <c r="G63" t="s">
+        <v>46</v>
+      </c>
+      <c r="H63" t="s">
+        <v>94</v>
+      </c>
+      <c r="I63" t="s">
+        <v>46</v>
+      </c>
+      <c r="J63" t="s">
+        <v>48</v>
+      </c>
+      <c r="K63" t="s">
+        <v>207</v>
+      </c>
+      <c r="L63" t="s">
+        <v>50</v>
+      </c>
+      <c r="M63" t="s">
+        <v>48</v>
+      </c>
+      <c r="N63" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="64" spans="1:14">
+      <c r="A64" t="s">
+        <v>208</v>
+      </c>
+      <c r="B64" t="s">
+        <v>193</v>
+      </c>
+      <c r="C64">
+        <v>3</v>
+      </c>
+      <c r="D64" t="s">
+        <v>59</v>
+      </c>
+      <c r="E64" t="s">
+        <v>194</v>
+      </c>
+      <c r="F64" t="s">
+        <v>46</v>
+      </c>
+      <c r="G64" t="s">
+        <v>46</v>
+      </c>
+      <c r="H64" t="s">
+        <v>94</v>
+      </c>
+      <c r="I64" t="s">
+        <v>46</v>
+      </c>
+      <c r="J64" t="s">
+        <v>48</v>
+      </c>
+      <c r="K64" t="s">
+        <v>209</v>
+      </c>
+      <c r="L64" t="s">
+        <v>50</v>
+      </c>
+      <c r="M64" t="s">
+        <v>48</v>
+      </c>
+      <c r="N64" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="65" spans="1:14">
+      <c r="A65" t="s">
+        <v>210</v>
+      </c>
+      <c r="B65" t="s">
+        <v>211</v>
+      </c>
+      <c r="C65">
+        <v>3</v>
+      </c>
+      <c r="D65" t="s">
+        <v>80</v>
+      </c>
+      <c r="E65" t="s">
+        <v>194</v>
+      </c>
+      <c r="F65" t="s">
+        <v>46</v>
+      </c>
+      <c r="G65" t="s">
+        <v>46</v>
+      </c>
+      <c r="H65" t="s">
+        <v>94</v>
+      </c>
+      <c r="I65" t="s">
+        <v>46</v>
+      </c>
+      <c r="J65" t="s">
+        <v>48</v>
+      </c>
+      <c r="K65" t="s">
+        <v>212</v>
+      </c>
+      <c r="L65" t="s">
+        <v>50</v>
+      </c>
+      <c r="M65" t="s">
+        <v>48</v>
+      </c>
+      <c r="N65" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="66" spans="1:14">
+      <c r="A66" t="s">
+        <v>213</v>
+      </c>
+      <c r="B66" t="s">
+        <v>214</v>
+      </c>
+      <c r="C66">
+        <v>3</v>
+      </c>
+      <c r="D66" t="s">
+        <v>59</v>
+      </c>
+      <c r="E66" t="s">
+        <v>215</v>
+      </c>
+      <c r="F66" t="s">
+        <v>46</v>
+      </c>
+      <c r="G66" t="s">
+        <v>46</v>
+      </c>
+      <c r="H66" t="s">
+        <v>94</v>
+      </c>
+      <c r="I66" t="s">
+        <v>46</v>
+      </c>
+      <c r="J66" t="s">
+        <v>95</v>
+      </c>
+      <c r="K66" t="s">
+        <v>96</v>
+      </c>
+      <c r="L66" t="s">
+        <v>46</v>
+      </c>
+      <c r="M66" t="s">
+        <v>97</v>
+      </c>
+      <c r="N66" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="67" spans="1:14">
+      <c r="A67" t="s">
+        <v>216</v>
+      </c>
+      <c r="B67" t="s">
+        <v>214</v>
+      </c>
+      <c r="C67">
+        <v>3</v>
+      </c>
+      <c r="D67" t="s">
+        <v>59</v>
+      </c>
+      <c r="E67" t="s">
+        <v>215</v>
+      </c>
+      <c r="F67" t="s">
+        <v>46</v>
+      </c>
+      <c r="G67" t="s">
+        <v>46</v>
+      </c>
+      <c r="H67" t="s">
+        <v>94</v>
+      </c>
+      <c r="I67" t="s">
+        <v>46</v>
+      </c>
+      <c r="J67" t="s">
+        <v>99</v>
+      </c>
+      <c r="K67" t="s">
+        <v>100</v>
+      </c>
+      <c r="L67" t="s">
+        <v>46</v>
+      </c>
+      <c r="M67" t="s">
+        <v>101</v>
+      </c>
+      <c r="N67" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="68" spans="1:14">
+      <c r="A68" t="s">
+        <v>217</v>
+      </c>
+      <c r="B68" t="s">
+        <v>214</v>
+      </c>
+      <c r="C68">
+        <v>3</v>
+      </c>
+      <c r="D68" t="s">
+        <v>59</v>
+      </c>
+      <c r="E68" t="s">
+        <v>215</v>
+      </c>
+      <c r="F68" t="s">
+        <v>46</v>
+      </c>
+      <c r="G68" t="s">
+        <v>46</v>
+      </c>
+      <c r="H68" t="s">
+        <v>94</v>
+      </c>
+      <c r="I68" t="s">
+        <v>46</v>
+      </c>
+      <c r="J68" t="s">
+        <v>103</v>
+      </c>
+      <c r="K68" t="s">
+        <v>104</v>
+      </c>
+      <c r="L68" t="s">
+        <v>46</v>
+      </c>
+      <c r="M68" t="s">
+        <v>105</v>
+      </c>
+      <c r="N68" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="69" spans="1:14">
+      <c r="A69" t="s">
+        <v>218</v>
+      </c>
+      <c r="B69" t="s">
+        <v>214</v>
+      </c>
+      <c r="C69">
+        <v>3</v>
+      </c>
+      <c r="D69" t="s">
+        <v>59</v>
+      </c>
+      <c r="E69" t="s">
+        <v>215</v>
+      </c>
+      <c r="F69" t="s">
+        <v>46</v>
+      </c>
+      <c r="G69" t="s">
+        <v>46</v>
+      </c>
+      <c r="H69" t="s">
+        <v>94</v>
+      </c>
+      <c r="I69" t="s">
+        <v>46</v>
+      </c>
+      <c r="J69" t="s">
+        <v>107</v>
+      </c>
+      <c r="K69" t="s">
+        <v>108</v>
+      </c>
+      <c r="L69" t="s">
+        <v>46</v>
+      </c>
+      <c r="M69" t="s">
+        <v>109</v>
+      </c>
+      <c r="N69" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="70" spans="1:14">
+      <c r="A70" t="s">
+        <v>219</v>
+      </c>
+      <c r="B70" t="s">
+        <v>214</v>
+      </c>
+      <c r="C70">
+        <v>3</v>
+      </c>
+      <c r="D70" t="s">
+        <v>59</v>
+      </c>
+      <c r="E70" t="s">
+        <v>215</v>
+      </c>
+      <c r="F70" t="s">
+        <v>46</v>
+      </c>
+      <c r="G70" t="s">
+        <v>46</v>
+      </c>
+      <c r="H70" t="s">
+        <v>94</v>
+      </c>
+      <c r="I70" t="s">
+        <v>46</v>
+      </c>
+      <c r="J70" t="s">
+        <v>111</v>
+      </c>
+      <c r="K70" t="s">
+        <v>112</v>
+      </c>
+      <c r="L70" t="s">
+        <v>46</v>
+      </c>
+      <c r="M70" t="s">
+        <v>113</v>
+      </c>
+      <c r="N70" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="71" spans="1:14">
+      <c r="A71" t="s">
+        <v>220</v>
+      </c>
+      <c r="B71" t="s">
+        <v>214</v>
+      </c>
+      <c r="C71">
+        <v>3</v>
+      </c>
+      <c r="D71" t="s">
+        <v>59</v>
+      </c>
+      <c r="E71" t="s">
+        <v>215</v>
+      </c>
+      <c r="F71" t="s">
+        <v>46</v>
+      </c>
+      <c r="G71" t="s">
+        <v>46</v>
+      </c>
+      <c r="H71" t="s">
+        <v>94</v>
+      </c>
+      <c r="I71" t="s">
+        <v>46</v>
+      </c>
+      <c r="J71" t="s">
+        <v>115</v>
+      </c>
+      <c r="K71" t="s">
+        <v>116</v>
+      </c>
+      <c r="L71" t="s">
+        <v>46</v>
+      </c>
+      <c r="M71" t="s">
+        <v>117</v>
+      </c>
+      <c r="N71" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="72" spans="1:14">
+      <c r="A72" t="s">
+        <v>221</v>
+      </c>
+      <c r="B72" t="s">
+        <v>214</v>
+      </c>
+      <c r="C72">
+        <v>3</v>
+      </c>
+      <c r="D72" t="s">
+        <v>59</v>
+      </c>
+      <c r="E72" t="s">
+        <v>215</v>
+      </c>
+      <c r="F72" t="s">
+        <v>46</v>
+      </c>
+      <c r="G72" t="s">
+        <v>46</v>
+      </c>
+      <c r="H72" t="s">
+        <v>94</v>
+      </c>
+      <c r="I72" t="s">
+        <v>46</v>
+      </c>
+      <c r="J72" t="s">
+        <v>119</v>
+      </c>
+      <c r="K72" t="s">
+        <v>120</v>
+      </c>
+      <c r="L72" t="s">
+        <v>46</v>
+      </c>
+      <c r="M72" t="s">
+        <v>121</v>
+      </c>
+      <c r="N72" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="73" spans="1:14">
+      <c r="A73" t="s">
+        <v>222</v>
+      </c>
+      <c r="B73" t="s">
+        <v>214</v>
+      </c>
+      <c r="C73">
+        <v>3</v>
+      </c>
+      <c r="D73" t="s">
+        <v>59</v>
+      </c>
+      <c r="E73" t="s">
+        <v>215</v>
+      </c>
+      <c r="F73" t="s">
+        <v>46</v>
+      </c>
+      <c r="G73" t="s">
+        <v>46</v>
+      </c>
+      <c r="H73" t="s">
+        <v>94</v>
+      </c>
+      <c r="I73" t="s">
+        <v>46</v>
+      </c>
+      <c r="J73" t="s">
+        <v>123</v>
+      </c>
+      <c r="K73" t="s">
+        <v>124</v>
+      </c>
+      <c r="L73" t="s">
+        <v>46</v>
+      </c>
+      <c r="M73" t="s">
+        <v>125</v>
+      </c>
+      <c r="N73" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="74" spans="1:14">
+      <c r="A74" t="s">
+        <v>223</v>
+      </c>
+      <c r="B74" t="s">
+        <v>224</v>
+      </c>
+      <c r="C74">
+        <v>3</v>
+      </c>
+      <c r="D74" t="s">
+        <v>44</v>
+      </c>
+      <c r="E74" t="s">
+        <v>215</v>
+      </c>
+      <c r="F74" t="s">
+        <v>46</v>
+      </c>
+      <c r="G74" t="s">
+        <v>46</v>
+      </c>
+      <c r="H74" t="s">
+        <v>94</v>
+      </c>
+      <c r="I74" t="s">
+        <v>46</v>
+      </c>
+      <c r="J74" t="s">
+        <v>48</v>
+      </c>
+      <c r="K74" t="s">
+        <v>225</v>
+      </c>
+      <c r="L74" t="s">
+        <v>50</v>
+      </c>
+      <c r="M74" t="s">
+        <v>48</v>
+      </c>
+      <c r="N74" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="75" spans="1:14">
+      <c r="A75" t="s">
+        <v>226</v>
+      </c>
+      <c r="B75" t="s">
+        <v>227</v>
+      </c>
+      <c r="C75">
+        <v>3</v>
+      </c>
+      <c r="D75" t="s">
+        <v>54</v>
+      </c>
+      <c r="E75" t="s">
+        <v>215</v>
+      </c>
+      <c r="F75" t="s">
+        <v>46</v>
+      </c>
+      <c r="G75" t="s">
+        <v>46</v>
+      </c>
+      <c r="H75" t="s">
+        <v>94</v>
+      </c>
+      <c r="I75" t="s">
+        <v>46</v>
+      </c>
+      <c r="J75" t="s">
+        <v>48</v>
+      </c>
+      <c r="K75" t="s">
+        <v>228</v>
+      </c>
+      <c r="L75" t="s">
+        <v>50</v>
+      </c>
+      <c r="M75" t="s">
+        <v>48</v>
+      </c>
+      <c r="N75" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="76" spans="1:14">
+      <c r="A76" t="s">
+        <v>229</v>
+      </c>
+      <c r="B76" t="s">
+        <v>214</v>
+      </c>
+      <c r="C76">
+        <v>3</v>
+      </c>
+      <c r="D76" t="s">
+        <v>59</v>
+      </c>
+      <c r="E76" t="s">
+        <v>215</v>
+      </c>
+      <c r="F76" t="s">
+        <v>46</v>
+      </c>
+      <c r="G76" t="s">
+        <v>46</v>
+      </c>
+      <c r="H76" t="s">
+        <v>94</v>
+      </c>
+      <c r="I76" t="s">
+        <v>46</v>
+      </c>
+      <c r="J76" t="s">
+        <v>48</v>
+      </c>
+      <c r="K76" t="s">
+        <v>230</v>
+      </c>
+      <c r="L76" t="s">
+        <v>50</v>
+      </c>
+      <c r="M76" t="s">
+        <v>48</v>
+      </c>
+      <c r="N76" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="77" spans="1:14">
+      <c r="A77" t="s">
+        <v>231</v>
+      </c>
+      <c r="B77" t="s">
+        <v>232</v>
+      </c>
+      <c r="C77">
+        <v>3</v>
+      </c>
+      <c r="D77" t="s">
+        <v>80</v>
+      </c>
+      <c r="E77" t="s">
+        <v>215</v>
+      </c>
+      <c r="F77" t="s">
+        <v>46</v>
+      </c>
+      <c r="G77" t="s">
+        <v>46</v>
+      </c>
+      <c r="H77" t="s">
+        <v>94</v>
+      </c>
+      <c r="I77" t="s">
+        <v>46</v>
+      </c>
+      <c r="J77" t="s">
+        <v>48</v>
+      </c>
+      <c r="K77" t="s">
+        <v>233</v>
+      </c>
+      <c r="L77" t="s">
+        <v>50</v>
+      </c>
+      <c r="M77" t="s">
+        <v>48</v>
+      </c>
+      <c r="N77" t="s">
+        <v>51</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/制造_躯体材料配置表_Manufacture_BodyPartConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/制造_躯体材料配置表_Manufacture_BodyPartConfig.xlsx
@@ -1353,9 +1353,15 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1708,6 +1714,7 @@
     <col min="1" max="1" width="24.625" customWidth="1"/>
     <col min="5" max="5" width="12.875" customWidth="1"/>
     <col min="8" max="8" width="48.75" customWidth="1"/>
+    <col min="12" max="12" width="9" style="2"/>
     <col min="13" max="13" width="26.875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1745,7 +1752,7 @@
       <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
       <c r="M1" t="s">
@@ -1789,7 +1796,7 @@
       <c r="K2" t="s">
         <v>24</v>
       </c>
-      <c r="L2" t="s">
+      <c r="L2" s="2" t="s">
         <v>25</v>
       </c>
       <c r="M2" t="s">
@@ -1833,7 +1840,7 @@
       <c r="K3" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="L3" s="1" t="s">
+      <c r="L3" s="3" t="s">
         <v>39</v>
       </c>
       <c r="M3" s="1" t="s">
@@ -1877,7 +1884,7 @@
       <c r="K4" t="s">
         <v>49</v>
       </c>
-      <c r="L4" t="s">
+      <c r="L4" s="2" t="s">
         <v>50</v>
       </c>
       <c r="M4" t="s">
@@ -1921,7 +1928,7 @@
       <c r="K5" t="s">
         <v>55</v>
       </c>
-      <c r="L5" t="s">
+      <c r="L5" s="2" t="s">
         <v>50</v>
       </c>
       <c r="M5" t="s">
@@ -1965,7 +1972,7 @@
       <c r="K6" t="s">
         <v>61</v>
       </c>
-      <c r="L6" t="s">
+      <c r="L6" s="2" t="s">
         <v>46</v>
       </c>
       <c r="M6" t="s">
@@ -2009,7 +2016,7 @@
       <c r="K7" t="s">
         <v>65</v>
       </c>
-      <c r="L7" t="s">
+      <c r="L7" s="2" t="s">
         <v>46</v>
       </c>
       <c r="M7" t="s">
@@ -2053,7 +2060,7 @@
       <c r="K8" t="s">
         <v>70</v>
       </c>
-      <c r="L8" t="s">
+      <c r="L8" s="2" t="s">
         <v>46</v>
       </c>
       <c r="M8" t="s">
@@ -2097,7 +2104,7 @@
       <c r="K9" t="s">
         <v>74</v>
       </c>
-      <c r="L9" t="s">
+      <c r="L9" s="2" t="s">
         <v>46</v>
       </c>
       <c r="M9" t="s">
@@ -2141,7 +2148,7 @@
       <c r="K10" t="s">
         <v>77</v>
       </c>
-      <c r="L10" t="s">
+      <c r="L10" s="2" t="s">
         <v>50</v>
       </c>
       <c r="M10" t="s">
@@ -2185,7 +2192,7 @@
       <c r="K11" t="s">
         <v>81</v>
       </c>
-      <c r="L11" t="s">
+      <c r="L11" s="2" t="s">
         <v>50</v>
       </c>
       <c r="M11" t="s">
@@ -2229,7 +2236,7 @@
       <c r="K12" t="s">
         <v>49</v>
       </c>
-      <c r="L12" t="s">
+      <c r="L12" s="2" t="s">
         <v>50</v>
       </c>
       <c r="M12" t="s">
@@ -2273,7 +2280,7 @@
       <c r="K13" t="s">
         <v>55</v>
       </c>
-      <c r="L13" t="s">
+      <c r="L13" s="2" t="s">
         <v>50</v>
       </c>
       <c r="M13" t="s">
@@ -2317,7 +2324,7 @@
       <c r="K14" t="s">
         <v>61</v>
       </c>
-      <c r="L14" t="s">
+      <c r="L14" s="2" t="s">
         <v>46</v>
       </c>
       <c r="M14" t="s">
@@ -2361,7 +2368,7 @@
       <c r="K15" t="s">
         <v>65</v>
       </c>
-      <c r="L15" t="s">
+      <c r="L15" s="2" t="s">
         <v>46</v>
       </c>
       <c r="M15" t="s">
@@ -2405,7 +2412,7 @@
       <c r="K16" t="s">
         <v>70</v>
       </c>
-      <c r="L16" t="s">
+      <c r="L16" s="2" t="s">
         <v>46</v>
       </c>
       <c r="M16" t="s">
@@ -2449,7 +2456,7 @@
       <c r="K17" t="s">
         <v>74</v>
       </c>
-      <c r="L17" t="s">
+      <c r="L17" s="2" t="s">
         <v>46</v>
       </c>
       <c r="M17" t="s">
@@ -2493,7 +2500,7 @@
       <c r="K18" t="s">
         <v>96</v>
       </c>
-      <c r="L18" t="s">
+      <c r="L18" s="2" t="s">
         <v>46</v>
       </c>
       <c r="M18" t="s">
@@ -2537,7 +2544,7 @@
       <c r="K19" t="s">
         <v>100</v>
       </c>
-      <c r="L19" t="s">
+      <c r="L19" s="2" t="s">
         <v>46</v>
       </c>
       <c r="M19" t="s">
@@ -2581,7 +2588,7 @@
       <c r="K20" t="s">
         <v>104</v>
       </c>
-      <c r="L20" t="s">
+      <c r="L20" s="2" t="s">
         <v>46</v>
       </c>
       <c r="M20" t="s">
@@ -2625,7 +2632,7 @@
       <c r="K21" t="s">
         <v>108</v>
       </c>
-      <c r="L21" t="s">
+      <c r="L21" s="2" t="s">
         <v>46</v>
       </c>
       <c r="M21" t="s">
@@ -2669,7 +2676,7 @@
       <c r="K22" t="s">
         <v>112</v>
       </c>
-      <c r="L22" t="s">
+      <c r="L22" s="2" t="s">
         <v>46</v>
       </c>
       <c r="M22" t="s">
@@ -2713,7 +2720,7 @@
       <c r="K23" t="s">
         <v>116</v>
       </c>
-      <c r="L23" t="s">
+      <c r="L23" s="2" t="s">
         <v>46</v>
       </c>
       <c r="M23" t="s">
@@ -2757,7 +2764,7 @@
       <c r="K24" t="s">
         <v>120</v>
       </c>
-      <c r="L24" t="s">
+      <c r="L24" s="2" t="s">
         <v>46</v>
       </c>
       <c r="M24" t="s">
@@ -2801,7 +2808,7 @@
       <c r="K25" t="s">
         <v>124</v>
       </c>
-      <c r="L25" t="s">
+      <c r="L25" s="2" t="s">
         <v>46</v>
       </c>
       <c r="M25" t="s">
@@ -2845,7 +2852,7 @@
       <c r="K26" t="s">
         <v>131</v>
       </c>
-      <c r="L26" t="s">
+      <c r="L26" s="2" t="s">
         <v>46</v>
       </c>
       <c r="M26" t="s">
@@ -2889,7 +2896,7 @@
       <c r="K27" t="s">
         <v>137</v>
       </c>
-      <c r="L27" t="s">
+      <c r="L27" s="2" t="s">
         <v>46</v>
       </c>
       <c r="M27" t="s">
@@ -2933,7 +2940,7 @@
       <c r="K28" t="s">
         <v>77</v>
       </c>
-      <c r="L28" t="s">
+      <c r="L28" s="2" t="s">
         <v>50</v>
       </c>
       <c r="M28" t="s">
@@ -2977,7 +2984,7 @@
       <c r="K29" t="s">
         <v>81</v>
       </c>
-      <c r="L29" t="s">
+      <c r="L29" s="2" t="s">
         <v>50</v>
       </c>
       <c r="M29" t="s">
@@ -3021,7 +3028,7 @@
       <c r="K30" t="s">
         <v>142</v>
       </c>
-      <c r="L30" t="s">
+      <c r="L30" s="2" t="s">
         <v>50</v>
       </c>
       <c r="M30" t="s">
@@ -3065,7 +3072,7 @@
       <c r="K31" t="s">
         <v>144</v>
       </c>
-      <c r="L31" t="s">
+      <c r="L31" s="2" t="s">
         <v>50</v>
       </c>
       <c r="M31" t="s">
@@ -3109,7 +3116,7 @@
       <c r="K32" t="s">
         <v>146</v>
       </c>
-      <c r="L32" t="s">
+      <c r="L32" s="2" t="s">
         <v>50</v>
       </c>
       <c r="M32" t="s">
@@ -3153,7 +3160,7 @@
       <c r="K33" t="s">
         <v>148</v>
       </c>
-      <c r="L33" t="s">
+      <c r="L33" s="2" t="s">
         <v>50</v>
       </c>
       <c r="M33" t="s">
@@ -3197,7 +3204,7 @@
       <c r="K34" t="s">
         <v>151</v>
       </c>
-      <c r="L34" t="s">
+      <c r="L34" s="2" t="s">
         <v>50</v>
       </c>
       <c r="M34" t="s">
@@ -3241,7 +3248,7 @@
       <c r="K35" t="s">
         <v>154</v>
       </c>
-      <c r="L35" t="s">
+      <c r="L35" s="2" t="s">
         <v>50</v>
       </c>
       <c r="M35" t="s">
@@ -3285,7 +3292,7 @@
       <c r="K36" t="s">
         <v>156</v>
       </c>
-      <c r="L36" t="s">
+      <c r="L36" s="2" t="s">
         <v>50</v>
       </c>
       <c r="M36" t="s">
@@ -3329,7 +3336,7 @@
       <c r="K37" t="s">
         <v>159</v>
       </c>
-      <c r="L37" t="s">
+      <c r="L37" s="2" t="s">
         <v>50</v>
       </c>
       <c r="M37" t="s">
@@ -3373,7 +3380,7 @@
       <c r="K38" t="s">
         <v>162</v>
       </c>
-      <c r="L38" t="s">
+      <c r="L38" s="2" t="s">
         <v>50</v>
       </c>
       <c r="M38" t="s">
@@ -3417,7 +3424,7 @@
       <c r="K39" t="s">
         <v>165</v>
       </c>
-      <c r="L39" t="s">
+      <c r="L39" s="2" t="s">
         <v>50</v>
       </c>
       <c r="M39" t="s">
@@ -3461,7 +3468,7 @@
       <c r="K40" t="s">
         <v>167</v>
       </c>
-      <c r="L40" t="s">
+      <c r="L40" s="2" t="s">
         <v>50</v>
       </c>
       <c r="M40" t="s">
@@ -3505,7 +3512,7 @@
       <c r="K41" t="s">
         <v>170</v>
       </c>
-      <c r="L41" t="s">
+      <c r="L41" s="2" t="s">
         <v>50</v>
       </c>
       <c r="M41" t="s">
@@ -3549,7 +3556,7 @@
       <c r="K42" t="s">
         <v>96</v>
       </c>
-      <c r="L42" t="s">
+      <c r="L42" s="2" t="s">
         <v>46</v>
       </c>
       <c r="M42" t="s">
@@ -3593,7 +3600,7 @@
       <c r="K43" t="s">
         <v>100</v>
       </c>
-      <c r="L43" t="s">
+      <c r="L43" s="2" t="s">
         <v>46</v>
       </c>
       <c r="M43" t="s">
@@ -3637,7 +3644,7 @@
       <c r="K44" t="s">
         <v>104</v>
       </c>
-      <c r="L44" t="s">
+      <c r="L44" s="2" t="s">
         <v>46</v>
       </c>
       <c r="M44" t="s">
@@ -3681,7 +3688,7 @@
       <c r="K45" t="s">
         <v>108</v>
       </c>
-      <c r="L45" t="s">
+      <c r="L45" s="2" t="s">
         <v>46</v>
       </c>
       <c r="M45" t="s">
@@ -3725,7 +3732,7 @@
       <c r="K46" t="s">
         <v>112</v>
       </c>
-      <c r="L46" t="s">
+      <c r="L46" s="2" t="s">
         <v>46</v>
       </c>
       <c r="M46" t="s">
@@ -3769,7 +3776,7 @@
       <c r="K47" t="s">
         <v>116</v>
       </c>
-      <c r="L47" t="s">
+      <c r="L47" s="2" t="s">
         <v>46</v>
       </c>
       <c r="M47" t="s">
@@ -3813,7 +3820,7 @@
       <c r="K48" t="s">
         <v>120</v>
       </c>
-      <c r="L48" t="s">
+      <c r="L48" s="2" t="s">
         <v>46</v>
       </c>
       <c r="M48" t="s">
@@ -3857,7 +3864,7 @@
       <c r="K49" t="s">
         <v>124</v>
       </c>
-      <c r="L49" t="s">
+      <c r="L49" s="2" t="s">
         <v>46</v>
       </c>
       <c r="M49" t="s">
@@ -3901,7 +3908,7 @@
       <c r="K50" t="s">
         <v>183</v>
       </c>
-      <c r="L50" t="s">
+      <c r="L50" s="2" t="s">
         <v>50</v>
       </c>
       <c r="M50" t="s">
@@ -3945,7 +3952,7 @@
       <c r="K51" t="s">
         <v>186</v>
       </c>
-      <c r="L51" t="s">
+      <c r="L51" s="2" t="s">
         <v>50</v>
       </c>
       <c r="M51" t="s">
@@ -3989,7 +3996,7 @@
       <c r="K52" t="s">
         <v>188</v>
       </c>
-      <c r="L52" t="s">
+      <c r="L52" s="2" t="s">
         <v>50</v>
       </c>
       <c r="M52" t="s">
@@ -4033,7 +4040,7 @@
       <c r="K53" t="s">
         <v>191</v>
       </c>
-      <c r="L53" t="s">
+      <c r="L53" s="2" t="s">
         <v>50</v>
       </c>
       <c r="M53" t="s">
@@ -4077,7 +4084,7 @@
       <c r="K54" t="s">
         <v>96</v>
       </c>
-      <c r="L54" t="s">
+      <c r="L54" s="2" t="s">
         <v>46</v>
       </c>
       <c r="M54" t="s">
@@ -4121,7 +4128,7 @@
       <c r="K55" t="s">
         <v>100</v>
       </c>
-      <c r="L55" t="s">
+      <c r="L55" s="2" t="s">
         <v>46</v>
       </c>
       <c r="M55" t="s">
@@ -4165,7 +4172,7 @@
       <c r="K56" t="s">
         <v>104</v>
       </c>
-      <c r="L56" t="s">
+      <c r="L56" s="2" t="s">
         <v>46</v>
       </c>
       <c r="M56" t="s">
@@ -4209,7 +4216,7 @@
       <c r="K57" t="s">
         <v>108</v>
       </c>
-      <c r="L57" t="s">
+      <c r="L57" s="2" t="s">
         <v>46</v>
       </c>
       <c r="M57" t="s">
@@ -4253,7 +4260,7 @@
       <c r="K58" t="s">
         <v>112</v>
       </c>
-      <c r="L58" t="s">
+      <c r="L58" s="2" t="s">
         <v>46</v>
       </c>
       <c r="M58" t="s">
@@ -4297,7 +4304,7 @@
       <c r="K59" t="s">
         <v>116</v>
       </c>
-      <c r="L59" t="s">
+      <c r="L59" s="2" t="s">
         <v>46</v>
       </c>
       <c r="M59" t="s">
@@ -4341,7 +4348,7 @@
       <c r="K60" t="s">
         <v>120</v>
       </c>
-      <c r="L60" t="s">
+      <c r="L60" s="2" t="s">
         <v>46</v>
       </c>
       <c r="M60" t="s">
@@ -4385,7 +4392,7 @@
       <c r="K61" t="s">
         <v>124</v>
       </c>
-      <c r="L61" t="s">
+      <c r="L61" s="2" t="s">
         <v>46</v>
       </c>
       <c r="M61" t="s">
@@ -4429,7 +4436,7 @@
       <c r="K62" t="s">
         <v>204</v>
       </c>
-      <c r="L62" t="s">
+      <c r="L62" s="2" t="s">
         <v>50</v>
       </c>
       <c r="M62" t="s">
@@ -4473,7 +4480,7 @@
       <c r="K63" t="s">
         <v>207</v>
       </c>
-      <c r="L63" t="s">
+      <c r="L63" s="2" t="s">
         <v>50</v>
       </c>
       <c r="M63" t="s">
@@ -4517,7 +4524,7 @@
       <c r="K64" t="s">
         <v>209</v>
       </c>
-      <c r="L64" t="s">
+      <c r="L64" s="2" t="s">
         <v>50</v>
       </c>
       <c r="M64" t="s">
@@ -4561,7 +4568,7 @@
       <c r="K65" t="s">
         <v>212</v>
       </c>
-      <c r="L65" t="s">
+      <c r="L65" s="2" t="s">
         <v>50</v>
       </c>
       <c r="M65" t="s">
@@ -4605,7 +4612,7 @@
       <c r="K66" t="s">
         <v>96</v>
       </c>
-      <c r="L66" t="s">
+      <c r="L66" s="2" t="s">
         <v>46</v>
       </c>
       <c r="M66" t="s">
@@ -4649,7 +4656,7 @@
       <c r="K67" t="s">
         <v>100</v>
       </c>
-      <c r="L67" t="s">
+      <c r="L67" s="2" t="s">
         <v>46</v>
       </c>
       <c r="M67" t="s">
@@ -4693,7 +4700,7 @@
       <c r="K68" t="s">
         <v>104</v>
       </c>
-      <c r="L68" t="s">
+      <c r="L68" s="2" t="s">
         <v>46</v>
       </c>
       <c r="M68" t="s">
@@ -4737,7 +4744,7 @@
       <c r="K69" t="s">
         <v>108</v>
       </c>
-      <c r="L69" t="s">
+      <c r="L69" s="2" t="s">
         <v>46</v>
       </c>
       <c r="M69" t="s">
@@ -4781,7 +4788,7 @@
       <c r="K70" t="s">
         <v>112</v>
       </c>
-      <c r="L70" t="s">
+      <c r="L70" s="2" t="s">
         <v>46</v>
       </c>
       <c r="M70" t="s">
@@ -4825,7 +4832,7 @@
       <c r="K71" t="s">
         <v>116</v>
       </c>
-      <c r="L71" t="s">
+      <c r="L71" s="2" t="s">
         <v>46</v>
       </c>
       <c r="M71" t="s">
@@ -4869,7 +4876,7 @@
       <c r="K72" t="s">
         <v>120</v>
       </c>
-      <c r="L72" t="s">
+      <c r="L72" s="2" t="s">
         <v>46</v>
       </c>
       <c r="M72" t="s">
@@ -4913,7 +4920,7 @@
       <c r="K73" t="s">
         <v>124</v>
       </c>
-      <c r="L73" t="s">
+      <c r="L73" s="2" t="s">
         <v>46</v>
       </c>
       <c r="M73" t="s">
@@ -4957,7 +4964,7 @@
       <c r="K74" t="s">
         <v>225</v>
       </c>
-      <c r="L74" t="s">
+      <c r="L74" s="2" t="s">
         <v>50</v>
       </c>
       <c r="M74" t="s">
@@ -5001,7 +5008,7 @@
       <c r="K75" t="s">
         <v>228</v>
       </c>
-      <c r="L75" t="s">
+      <c r="L75" s="2" t="s">
         <v>50</v>
       </c>
       <c r="M75" t="s">
@@ -5045,7 +5052,7 @@
       <c r="K76" t="s">
         <v>230</v>
       </c>
-      <c r="L76" t="s">
+      <c r="L76" s="2" t="s">
         <v>50</v>
       </c>
       <c r="M76" t="s">
@@ -5089,7 +5096,7 @@
       <c r="K77" t="s">
         <v>233</v>
       </c>
-      <c r="L77" t="s">
+      <c r="L77" s="2" t="s">
         <v>50</v>
       </c>
       <c r="M77" t="s">
